--- a/saida/produtos_enriquecidos_parte_5.xlsx
+++ b/saida/produtos_enriquecidos_parte_5.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,12 +549,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Dimensões: 88mm x 30mm; Material: aço SAE 1010; Acabamento: zincado</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.mercadolivre.com.br/fecho-trinco-chato-pcadeado-n2-88mm-x-30mm-zincado-inca/up/MLBU796959754</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -562,7 +562,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://cdn.construja.com.br/produtos/15494/15494.jpg | https://http2.mlstatic.com/D_Q_NP_2X_765084-MLB92795301494_092025-P.webp | https://http2.mlstatic.com/D_NQ_NP_923848-MLA108486201602_032026-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -736,17 +740,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>A Floreira Tripe é um suporte para plantas com design em tripé, fabricado em materiais resistentes. Ideal para decorar ambientes internos e externos, proporcionando estabilidade e estilo.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Peso: Não especificado. Material: Não especificado. Cor: Disponível em várias opções. Pegada: Opção de escolha.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.wjfundidos.com.br/detalhes-do-produto/1426/Floreira-tripe</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -754,7 +758,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.wjfundidos.com.br/produtos/4e31__.jpg | https://down-br.img.susercontent.com/file/br-11134207-81z1k-mgmofv72khkwd8 | https://www.unifermoveis.com.br/wp-content/uploads/2022/10/Floreira-Tripe-2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -789,7 +797,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Calibres disponíveis: 24 (0,65mm) e 26 (0,5mm). Desenvolvimentos de 16, 25, 33, 50 e 100cm. Deve ser isenta de ferrugem e fissuras nas bordas.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -799,10 +807,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>https://telhacerta.com.br/storage/downloads/arquivo-3-20221121144843637bb9fb79b53.pdf</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/743700/180_chapa_galvanizada_rusbruto_1_metro_de_comprimento_151_1_c5a11bd2a81bc503fe27693152f28dc7.jpg | https://t74920.vteximg.com.br/arquivos/ids/164008/chapa-galvanizada.jpg?v=637751894212070000 | https://originalacos.com.br/informacoes/images/chapa-galvanizada-com-espessura-reforcada.webp</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1077,7 +1089,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Altura: 108 cm, Material: Não especificado no contexto.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1090,7 +1102,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://elecon.com.br/wp-content/uploads/2025/05/CURVA-CURTA-PE-COLUNA-SILENTIUM-Media.jpeg | https://mediahub.wavin.com/transform/c052ca23-2b44-4e71-b6c3-b1861ffc0a7c/14874-CURVA-CTA-PE-COLUNA-ESG-SR-DN150</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1120,14 +1136,10 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+          <t>FF FLORAO N.00 é um produto floral, possivelmente um facilitador para passar roupas ou um fertilizante líquido.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -1138,7 +1150,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/1593/1593430/produto/163983691/finishfresh_floral_1l_frente_novo-ucywym.jpg | http://www.lojadoprofissional.com.br/cdn/imagens/produtos/det/finisher-fresh-floral-facilitador-para-passar-roupas-5-litros-spartan-51222dab9089117b0e10fcf406336159.jpg | https://www.gardencidadedasflores.com.br/public/produtos/360/360-hydrofert-floral-120ml-n-00-p-14-k-13_m.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1216,7 +1232,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FF FLORAO N.02 MEDIO 42 X 15 CM. Produto não encontrado na web.</t>
+          <t>FF FLORAO N.02 MEDIO 42 X 15 CM é um produto floral, provavelmente um arranjo ou vaso de flores de tamanho médio com dimensões 42 x 15 cm.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1234,7 +1250,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://acdn-us.mitiendanube.com/stores/001/448/605/products/flora-2-356d73bbd3be2df06b17132146213026-480-0.webp | https://www.tiktok.com/api/img/?itemId=7611179042087259410&amp;location=0&amp;aid=1988 | https://http2.mlstatic.com/D_NQ_NP_640159-MLA104278528987_012026-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2037,12 +2057,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Dimensões: 86x15cm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.carrefour.com.br/produto/grade-ferro-fundido-flor-de-liz-inclinada-varanda-xcm-324849768</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2050,7 +2070,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://carrefourbr.vtexassets.com/arquivos/ids/103112201-848-848/56b6916f6cf64290b3a7af3434a2a5b2.jpg?v=638128411829000000 | https://images.tcdn.com.br/img/img_prod/148301/grade_flor_liz_inclinada_em_ferro_fundido_1547_2_eb5ad11c8427db9e441ad9e70d6d13c9.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2176,7 +2200,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FF GRADE GREGA 82 X 16CM. Produto não encontrado na web.</t>
+          <t>FF GRADE GREGA 82 X 16CM é uma grade de ferro fundido com design grego, ideal para uso em jardins, calçadas e áreas externas.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2194,7 +2218,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_grega_em_ferro_fundido_1552_2_0be7a1fc6248cdc5d5b42b559b7b3043.png | https://images.tcdn.com.br/img/img_prod/148301/grade_grega_em_ferro_fundido_1552_1_c4fc65dadb647182ed4c8243e3577d4a.png</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2464,17 +2492,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>O Jacaré MPM é um guarda-corpo temporário simples e eficiente, projetado para proteger a periferia de obras de construção. O sistema utiliza dentes de aço galvanizado para fixação na laje, dispensando acessórios adicionais.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Sistema de fixação com dentes de aço galvanizado, instalação rápida (menos de 10 minutos), não requer acessórios adicionais, mais de 250 obras atendidas com sucesso.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://jacarempm.com.br/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2482,7 +2510,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1108186/1697553826_logotipo-da-loja-1.png | https://cdn.awsli.com.br/1030/1030675/produto/344137329/55e23c9dc5f24e6c792a6506becc8907-9dldusb1uu.jpg | https://http2.mlstatic.com/D_Q_NP_2X_727348-MLB110174449730_042026-P.webp</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2517,7 +2549,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Material: Ferro fundido; Cor: Ouro preto; Aplicação: Proteção e decoração de ambientes.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2530,7 +2562,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_em_ferro_fundido_1571_2_4d9fa8daaca9fb91bb740102a4c3bb73.png | https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_em_ferro_fundido_1571_1_8888ee5312d9569bc4c747d453ab705a.png</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2565,7 +2601,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Material: Ferro fundido; Cor: Ouro preto; Grau de inclinação: 1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2578,7 +2614,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_com_1_grau_em_ferro_fundido_1570_1_657a55950c9aec2de30ac114a7077dd3.png | https://d5gag3xtge2og.cloudfront.net/producao/33580712/M/grade-imperial-pequena-16x50.webp</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2613,7 +2653,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Material: Ferro fundido; Cor: Ouro preto; Grau: 2; Dimensões: 101x15cm.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2626,7 +2666,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://cdn.leroymerlin.com.br/products/grade_ferro_fundido_ouro_preto_2_grau_sacada_escada_101x15cm_1567880811_5be1_600x600.jpg | https://cdn.leroymerlin.com.br/products/grade_ferro_fundido_ouro_preto_2_grau_sacada_escada_101x15cm_1567880811_4c5f_600x600.jpg | https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_em_ferro_fundido_1571_1_8888ee5312d9569bc4c747d453ab705a.png</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2661,7 +2705,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Estrutura metálica, geralmente em ferro fundido, com design retangular ou arqueado, adequada para suporte de videiras. Dimensões variam conforme a necessidade do cultivo.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2674,7 +2718,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://dcdn-us.mitiendanube.com/stores/002/503/307/products/arte-para-produtos-9e1852a12cc51e50a517186442082954-1024-1024.webp | http://dcdn-us.mitiendanube.com/stores/002/503/307/products/grade-parreira-uva-reta-406a64cb1956204e3317123426610551-640-0.webp | https://images.tcdn.com.br/img/img_prod/148301/180_grade_parreira_uva_em_ferro_fundido_1574_2_9511bcd135da178ab31c74cb646a0e92.png</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2995,22 +3043,22 @@
           <t>FF GRADE ROSACEA, um produto cujas informações específicas não foram encontradas.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>http://www.rosacea.org/physicians/grading-system-for-rosacea/view-online</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>http://www.rosacea.org/physicians/grading-system-for-rosacea/view-online</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://m.magazineluiza.com.br/a-static/420x420/prosacea-creme-facial-rosacea-21-25g/h2cshop/123p/a44fc1d34ea514ffd5b0ac51e913cc49.jpg | https://mc-df05ef79-e68e-4c65-8ea2-953494-cdn-endpoint.azureedge.net/-/media/gdm/us-branded/finacea/consumer/finacea-product-grey.jpg?rev=9d50e20b45204ed5a5155ef9722f637d | https://www.farmaciaeficacia.com.br/media/catalog/product/cache/33412c801b30787ffde781956b410354/c/r/creme-para-rosacea.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3328,17 +3376,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FF PE DE BANCO CAVALO 9 RIPAS. Produto não encontrado na web.</t>
+          <t>Par de pé de banco cavalo de ferro fundido, confeccionado em ferro fundido de alta qualidade, projetado para garantir durabilidade e estilo na montagem de móveis.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Altura do Assento: 40cm, Altura do Encosto: 77cm, Largura do Assento: 33cm, Peso: 15,2Kg, Itens Inclusos: 01 Par de Pé de Banco</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.mercadolivre.com.br/par-de-pe-de-banco-cavalo-de-ferro-fundido-9-furos-preto-pre/up/MLBU4261727100</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3346,7 +3394,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://cdn.leroymerlin.com.br/products/par_de_pe_de_banco_cavalo_de_ferro_fundido_1568019663_bf9d_600x600.jpg | https://cdn.leroymerlin.com.br/products/par_de_pe_de_banco_cavalo_de_ferro_fundido_1568019663_c3b8_600x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3381,12 +3433,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Altura do Assento: 22cm, Altura do Encosto: 43cm, Largura do Assento: 22cm, Quantidade de Réguas: 7, Peso: 8Kg (PAR)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.alumifundidos.com.br/detalhes-do-produto/147/pe-de-banco-ferro-fundido-frances-infantil</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3394,7 +3446,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://carrefourbr.vtexassets.com/arquivos/ids/215018315-848-848/image-0.jpg?v=639154956550700000 | https://carrefourbr.vtexassets.com/arquivos/ids/215018319-848-848/image-1.jpg?v=639154956552600000 | https://carrefourbr.vtexassets.com/arquivos/ids/215018324-848-848/image-2.jpg?v=639154956554930000</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3424,12 +3480,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FF PINHA 16 1/2 CM ( 3 ). Produto não encontrado na web.</t>
+          <t>FF PINHA 16 1/2 CM (3) é uma peça de ferro fundido com 16,5 cm de comprimento, utilizada em aplicações de construção e engenharia.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Comprimento: 16,5 cm; Material: Ferro Fundido; Quantidade: 3 peças</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3442,7 +3498,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.fionafranchimon.com/cdn/shop/files/135.png?v=1764068511&amp;width=1445 | https://images.tcdn.com.br/img/img_prod/148301/180_pinha_no_16_soldada_em_ferro_fundido_51053_1_7bbe85e0be9a371630f51c2b1f4f8ef7.png | https://http2.mlstatic.com/D_NQ_NP_862583-MLB115037567530_082026-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3477,7 +3537,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Material: Ferro fundido; Tamanho: 18 1/2 CM; Quantidade: 6 unidades por pacote.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3490,7 +3550,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/pinha_no_18_torcida_em_ferro_fundido_90365_2_2c4c2442f722f903f3aead2f6d43e971.png | https://images.tcdn.com.br/img/img_prod/148301/pinha_no_17_em_ferro_fundido_51194_1_416ec7dcd64fbca8b49bd41541346d11.png</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3573,7 +3637,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Diâmetro: 31 cm, Quantidade: 08 peças, Material: Ferro Fundido</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3586,7 +3650,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/pinha_no_02_macica_em_ferro_fundido_1775_1_608ca08180d2ae0a60e27711cb62da9e.png | https://images.tcdn.com.br/img/img_prod/148301/90_pinha_no_03_soldada_em_ferro_fundido_1769_2_53f51b43c2a2ec9900bc6cb356e3bbbb.png</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3616,17 +3684,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FF PINHA 36 CM (10 unidades). Produto não encontrado na web.</t>
+          <t>Pinha Enjoy de 36 cm, com 2 jatos (efeito chuva e cascata), em branco e cromado. Ideal para instalação mural.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Comprimento: 200 mm, Largura: 200 mm, Altura: 80 mm, Peso: 0.44 kg, Material: ABS, Estilo: Contemporâneo, Formato: Quadrangular, Tipologia de Instalação: Mural, Coleção: Enjoy</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://sanindusa.com/pt/produto/pinha-enjoy/ficha-tecnica?ref=5889210</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3634,7 +3702,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://acdn-us.mitiendanube.com/stores/001/272/619/products/imagem-do-whatsapp-de-2025-07-29-as-15-03-50_41ff47c1-94526cd20b9e186c8417538123802836-1024-1024.webp?utm_source=organic&amp;utm_campaign=&amp;utm_medium=&amp;utm_content=&amp;utm_term=&amp;subid=&amp;subid3=&amp;subid4=&amp;subid5=&amp;xcod=&amp;sck= | https://cdn.dooca.store/1056/products/1-pinha.jpg?v=1725038173 | https://images.tcdn.com.br/img/img_prod/148301/pinha_no_01_macica_em_ferro_fundido_1766_2_e57f162fda65bd2e4d513b886f48f704.png</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">

--- a/saida/produtos_enriquecidos_parte_5.xlsx
+++ b/saida/produtos_enriquecidos_parte_5.xlsx
@@ -3739,11 +3739,7 @@
           <t>FF PINHA 9 1/2 CM ( 2 ). Parece ser um produto relacionado a decoração ou artesanato, mas informações adicionais não foram encontradas.</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -3835,11 +3831,7 @@
           <t>FF ROSACEA FLOR DE LIRIO 13,5 é um produto relacionado a cuidados com a pele, especificamente para tratamento de rosácea.</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -3926,16 +3918,8 @@
           <t>P.E.</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>FF ROSACEA IMPERIAL 10 CM. Produto não encontrado na web.</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -3979,11 +3963,7 @@
           <t>FF ROSACEA IMPERIAL 12CM, um produto cujas informações não foram encontradas.</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4027,11 +4007,7 @@
           <t>FF ROSACEA IMPERIAL 15CM, um produto cujas informações não foram encontradas.</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4075,11 +4051,7 @@
           <t>FF ROSACEA IMPERIAL 18CM, um produto cujas informações específicas não foram encontradas.</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4267,11 +4239,7 @@
           <t>Martelo rompedor Vonder MRV 1500, 220V.</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4315,11 +4283,7 @@
           <t>Parafuso para concreto PCE 12 100, utilizado em aplicações que exigem fixação em concreto.</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8203,11 +8167,7 @@
           <t>Telha encanada galvanizada trapezoidal pintada branca, com uma face.</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8251,11 +8211,7 @@
           <t>Telha encanada galvanizada trapezoidal pintada branca com 02 faces.</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8299,11 +8255,7 @@
           <t>Telha encoberta pintada na cor laranja, com 2 faces.</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8347,11 +8299,7 @@
           <t>Telha encoberta termo isopor, um material de construção leve e isolante.</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8491,11 +8439,7 @@
           <t>Telha de isopor termoencapada, pintada de branco em uma face.</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8539,11 +8483,7 @@
           <t>Telha de isopor termoacústica pintada de branco em duas faces.</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8587,11 +8527,7 @@
           <t>Telha forro de isopor pintada com duas faces na cor branca.</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8635,11 +8571,7 @@
           <t>Telha galvanizada trapezoidal pintada na cor preta, com uma face visível.</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8822,16 +8754,8 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. A busca retornou um erro.</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8971,11 +8895,7 @@
           <t>Não foi possível obter informações sobre o produto devido a um erro na busca.</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9062,16 +8982,8 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9259,11 +9171,7 @@
           <t>Caderno universitário para anotações e estudos.</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9307,11 +9215,7 @@
           <t>Calculadora Bobina HR 150 Casio, uma calculadora de bobina com funções básicas para uso comercial e financeiro.</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9355,11 +9259,7 @@
           <t>Calculadora Bobina HR 150 Casio O NC, um modelo de calculadora com bobina para uso em escritórios e comércio.</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9403,11 +9303,7 @@
           <t>Calculadora BPBINA HR150 com caso de proteção.</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9547,11 +9443,7 @@
           <t>Cloro ativo 500 da marca Veja, produto utilizado para limpeza e desinfecção.</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9595,11 +9487,7 @@
           <t>Não foi possível obter informações sobre o produto devido a um erro na busca.</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9643,11 +9531,7 @@
           <t>O produto é um complemento de imposto, mas não foram encontradas informações detalhadas.</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9686,16 +9570,8 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9787,11 +9663,7 @@
           <t>Crédito de ICMS é um benefício fiscal que permite a compensação de valores pagos a título de ICMS.</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10075,11 +9947,7 @@
           <t>O produto trata-se de um serviço ou software relacionado à devolução de ICMS da substituição tributária.</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10123,11 +9991,7 @@
           <t>Não foi possível obter informações sobre o produto.</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10171,11 +10035,7 @@
           <t>Espuma multiuso L4, ideal para limpeza de diversas superfícies.</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10219,11 +10079,7 @@
           <t>Espoja multiuso L4 PG3 Brilhus Bettanin, ideal para limpeza pesada e duradoura.</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10267,11 +10123,7 @@
           <t>Grampeador Eagle 208, um dispositivo de escritório para grampear papéis.</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10459,11 +10311,7 @@
           <t>Não foi possível obter informações sobre o produto devido a um erro na busca.</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10507,11 +10355,7 @@
           <t>O produto é um material de uso e consumo, mas informações específicas não foram encontradas.</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10651,11 +10495,7 @@
           <t>Oodorizador de ambiente, produto para eliminar odores e deixar um aroma agradável.</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11078,16 +10918,8 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11179,11 +11011,7 @@
           <t>Sabonete líquido em embalagem de 5 litros.</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11227,11 +11055,7 @@
           <t>Saco de lixo pesado, vendido em pacotes com 100 unidades.</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11371,11 +11195,7 @@
           <t>Não foi possível obter informações sobre o produto devido a um erro na busca.</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11419,11 +11239,7 @@
           <t>Taxa de entrega, geralmente associada a custos de envio de produtos em compras online.</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11467,11 +11283,7 @@
           <t>Teclado USB para jogos, com conectividade USB.</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11515,11 +11327,7 @@
           <t>Telefone fio pleno preto da marca Intelbras.</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
           <t>Não encontrado</t>

--- a/saida/produtos_enriquecidos_parte_5.xlsx
+++ b/saida/produtos_enriquecidos_parte_5.xlsx
@@ -514,7 +514,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://paraferro.com.br/loja/wp-content/uploads/2019/08/Tela-soldada-tipo-Q-768x960.png | https://plataformaamtres.vtexassets.com/arquivos/ids/155974-800-800?v=638580507706470000&amp;width=800&amp;height=800&amp;aspect=true | https://http2.mlstatic.com/D_NQ_NP_613269-MLB51673624529_092022-O.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -564,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://cdn.construja.com.br/produtos/15494/15494.jpg | https://http2.mlstatic.com/D_Q_NP_2X_765084-MLB92795301494_092025-P.webp | https://http2.mlstatic.com/D_NQ_NP_923848-MLA108486201602_032026-O.webp</t>
+          <t>https://cdn.construja.com.br/produtos/15494/15494.jpg | https://http2.mlstatic.com/D_Q_NP_2X_765084-MLB92795301494_092025-P.webp | https://http2.mlstatic.com/D_NQ_NP_923848-MLA108486201602_032026-O.webp | https://images.tcdn.com.br/img/img_prod/1086068/fecho_trinco_chato_para_cadeado_n_2_inca_265674_1_bd8b545eaaeb4cead0439c9dc572b985.png | https://images.tcdn.com.br/img/img_prod/1100542/kit_fecho_trinco_chato_2_inox_02_pc_bom_2704_10_un_bomvink_45148_4_d282011151e5b93160d539fc7b98a577.jpg | https://images.tcdn.com.br/img/img_prod/1100542/kit_fecho_trinco_chato_2_inox_02_pc_bom_2704_5_un_bomvink_45146_2_52adcfe88238e0d5497b3ce6caf2f9d9.jpg</t>
         </is>
       </c>
     </row>
@@ -662,7 +666,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/628166/tubo_quadrado_150_x_150mm_15cmx15cm_metalon_4561_2_2296dd82545010e7169e1c92bf898974.jpg | https://www.firsteel.com.br/wp-content/uploads/2023/10/metalon-medidas.webp | https://projetarmateriais.oiapp.com.br/_core/_uploads/203/2024/07/1738160724jah7b5deg0.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -710,7 +718,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://armazemcoral.agilecdn.com.br/744778.jpg | https://product-hub-prd.madeiramadeira.com.br/876648675/images/4778d210-c80e-425e-83e1-284ad539b1b0fa6bd8fee9587674c4e16bf136.jpg | https://images.tcdn.com.br/img/img_prod/1326454/vassoura_para_jardim_plastica_22_dentes_com_cabo_famastil_7203_3_a37fcdc87c55c83aebbae818bb06cedb.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -760,7 +772,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.wjfundidos.com.br/produtos/4e31__.jpg | https://down-br.img.susercontent.com/file/br-11134207-81z1k-mgmofv72khkwd8 | https://www.unifermoveis.com.br/wp-content/uploads/2022/10/Floreira-Tripe-2.jpg</t>
+          <t>https://www.wjfundidos.com.br/produtos/4e31__.jpg | https://down-br.img.susercontent.com/file/br-11134207-81z1k-mgmofv72khkwd8 | https://www.unifermoveis.com.br/wp-content/uploads/2022/10/Floreira-Tripe-2.jpg | https://http2.mlstatic.com/D_NQ_NP_767687-MLB89225330586_082025-O-floreira-tripe-pequeno-p-jardim-vertical-porta-vaso.webp | https://down-br.img.susercontent.com/file/br-11134207-7r98o-lryiql8gb9d031 | https://http2.mlstatic.com/D_NQ_NP_911643-MLB76360114859_052024-O.webp</t>
         </is>
       </c>
     </row>
@@ -862,7 +874,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_653133-MLB51246009606_082022-O.webp | https://cdn.habitium.com/1135198/lanterna-em-chapa-de-aco-com-acabamento-em-preto-greenice-pintado-no-forno.jpg?sto=true&amp;width=480 | https://http2.mlstatic.com/D_NQ_NP_711863-MLB75259247267_032024-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -910,7 +926,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_632547-MLB69202589907_052023-O-chapa-ps-poliestireno-led-luminaria-branco-200x100-2mm.webp | https://http2.mlstatic.com/D_NQ_NP_711863-MLB75259247267_032024-O.webp | https://cdn.habitium.com/1135198/lanterna-em-chapa-de-aco-com-acabamento-em-preto-greenice-pintado-no-forno.jpg?sto=true&amp;width=480</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -958,7 +978,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1184849/ferragem_coluna_10x15_3_8_3_50_metros_fabrica_constrular_1375_1_d5703c1b02507c7479bc0db155604353.jpg | https://www.fundicaouniao.com.br/produtos/bf79_prod.jpg | https://www.properfilaluminio.com.br/storage/2023/04/28-547.png?v=1682303791</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1006,7 +1030,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/800x800/577/577557/produto/219200358/ld-2-cu7xbesn3o.png | https://cdn.awsli.com.br/2500x2500/577/577557/produto/219200358/sobre-coluna-frontal-sc-r-112113-intercooler--2--jhgm20al02.jpg | https://www.fundicaouniao.com.br/produtos/bf79_prod.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1054,7 +1082,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://3.bp.blogspot.com/-CMjCIEQAhUA/W8457Obl0mI/AAAAAAAAAT4/zWj4H1b0mFUPNu_C9qofA-WtIGE3LV4zACLcBGAs/s1600/Sapata+e+coluna.jpg | https://d5gag3xtge2og.cloudfront.net/producao/33580559/G/file_e281d569bccd54bb13d4d41dbc90f9a4.webp | https://http2.mlstatic.com/D_NQ_NP_830810-MLU78364820739_082024-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1104,7 +1136,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://elecon.com.br/wp-content/uploads/2025/05/CURVA-CURTA-PE-COLUNA-SILENTIUM-Media.jpeg | https://mediahub.wavin.com/transform/c052ca23-2b44-4e71-b6c3-b1861ffc0a7c/14874-CURVA-CTA-PE-COLUNA-ESG-SR-DN150</t>
+          <t>https://elecon.com.br/wp-content/uploads/2025/05/CURVA-CURTA-PE-COLUNA-SILENTIUM-Media.jpeg | https://mediahub.wavin.com/transform/c052ca23-2b44-4e71-b6c3-b1861ffc0a7c/14874-CURVA-CTA-PE-COLUNA-ESG-SR-DN150 | https://elecon.com.br/wp-content/uploads/2025/05/CURVA-CURTA-PE-COLUNA-ESGOTO-SERIE-REFORCADA-600x600.jpg | https://dimensaoincendio.com.br/wp-content/uploads/2019/08/19185-curva-ff-minR-min.png</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1184,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://cdn.awsli.com.br/1593/1593430/produto/163983691/finishfresh_floral_1l_frente_novo-ucywym.jpg | http://www.lojadoprofissional.com.br/cdn/imagens/produtos/det/finisher-fresh-floral-facilitador-para-passar-roupas-5-litros-spartan-51222dab9089117b0e10fcf406336159.jpg | https://www.gardencidadedasflores.com.br/public/produtos/360/360-hydrofert-floral-120ml-n-00-p-14-k-13_m.jpg</t>
+          <t>https://cdn.awsli.com.br/1593/1593430/produto/163983691/finishfresh_floral_1l_frente_novo-ucywym.jpg | http://www.lojadoprofissional.com.br/cdn/imagens/produtos/det/finisher-fresh-floral-facilitador-para-passar-roupas-5-litros-spartan-51222dab9089117b0e10fcf406336159.jpg | https://www.gardencidadedasflores.com.br/public/produtos/360/360-hydrofert-floral-120ml-n-00-p-14-k-13_m.jpg | http://dcdn-us.mitiendanube.com/stores/002/503/307/products/florao_21-cf1abace1ed5134f9316680043725092-640-0.webp | https://cdn.awsli.com.br/600x700/1977/1977919/produto/190808209/e1e023c1e4.jpg | https://vidaflora.mx/cdn/shop/files/bote-flora-codigo.png?v=1701881026&amp;width=1646</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1234,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://product-hub-prd.madeiramadeira.com.br/889937301/images/d8348392-3a13-440b-983f-f5378c8248c3102342e0standardresolution.jpg | https://cdn.leroymerlin.com.br/products/florao_pequeno_ornamento_em_ferro_fundido_decoracao_36x16cm_1570582224_12fd_300x300.jpg | http://dcdn-us.mitiendanube.com/stores/002/503/307/products/florao_21-cf1abace1ed5134f9316680043725092-640-0.webp</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1252,7 +1288,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://acdn-us.mitiendanube.com/stores/001/448/605/products/flora-2-356d73bbd3be2df06b17132146213026-480-0.webp | https://www.tiktok.com/api/img/?itemId=7611179042087259410&amp;location=0&amp;aid=1988 | https://http2.mlstatic.com/D_NQ_NP_640159-MLA104278528987_012026-O.webp</t>
+          <t>https://acdn-us.mitiendanube.com/stores/001/448/605/products/flora-2-356d73bbd3be2df06b17132146213026-480-0.webp | https://www.tiktok.com/api/img/?itemId=7611179042087259410&amp;location=0&amp;aid=1988 | https://http2.mlstatic.com/D_NQ_NP_640159-MLA104278528987_012026-O.webp | https://dcdn-us.mitiendanube.com/stores/002/503/307/products/florao_71-686e7042dfcf5f828516680036676814-480-0.webp | http://dcdn-us.mitiendanube.com/stores/002/503/307/products/florao_21-cf1abace1ed5134f9316680043725092-640-0.webp | https://dcdn-us.mitiendanube.com/stores/002/503/307/products/florao_41-03814c9ac39e453a5816680042295685-640-0.webp</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1338,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://avipecprodutos.fbitsstatic.net/img/p/floreira-n-03-preta-plasgarden-ref-732-73577/260138-1.jpg?w=520&amp;h=520&amp;v=no-change&amp;qs=ignore | https://cdn.leroymerlin.com.br/products/florao_grande_ornamento_em_ferro_fundido_decoracao_57x38cm_1570580337_d18f_600x600.jpg | http://dcdn-us.mitiendanube.com/stores/002/503/307/products/florao_21-cf1abace1ed5134f9316680043725092-640-0.webp</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1350,7 +1390,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://anfermoda.com/extras/imagenes/2023/Diadema5Florescaprimarfil547132anfermoda.jpg | https://anfermoda.com/extras/imagenes/2023/Diadema5Florescapri547132anfermoda.jpg | https://fitflamc.com/wp-content/uploads/2022/01/FELPA-FLOR-AGOTADA.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1398,7 +1442,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://d5gag3xtge2og.cloudfront.net/producao/33580753/G/file_c8c31844a0fe859beb565be15fa5faee.webp | https://http2.mlstatic.com/D_NQ_NP_680117-MLB80395730008_112024-O.webp | https://tampaoegrelhagk.com.br/cdn/shop/files/Grade-de-Ferro-Fundido-Abacaxi-Reta-14X81-cm_1024x1024.webp?v=1774618757</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1494,7 +1542,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://product-hub-prd.madeiramadeira.com.br/174890778/images/2f6027a0-8644-4af2-917e-e67ee56213ec2083bb57standardresolution.jpg | https://http2.mlstatic.com/D_NQ_NP_866198-MLB82584981155_022025-O.webp | https://http2.mlstatic.com/D_NQ_NP_928888-MLB70421579235_072023-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1542,7 +1594,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://fundicaoalfa.com.br/wp-content/uploads/2026/01/01-33.png | https://static.wixstatic.com/media/35a2ed_4aba08d7b8ff4bb499960c5f37a23241~mv2.jpg/v1/fill/w_2500,h_1666,al_c/35a2ed_4aba08d7b8ff4bb499960c5f37a23241~mv2.jpg | http://swaroza.com/cdn/shop/files/image_1080_6_461ac549-86b0-4b0a-b900-e2d84e32c557.webp?v=1734006989&amp;width=2048</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1590,7 +1646,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_982746-MLB80509365368_112024-O.webp | https://http2.mlstatic.com/D_NQ_NP_855750-MLB85610146984_062025-O.webp | https://dcdn-us.mitiendanube.com/stores/002/503/307/products/grade-bombe-curva-estreita-a262f8ee4c5429e7e917123414219305-480-0.webp</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1638,7 +1698,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/sg-11134201-7rfgu-m30p1xrbke264b | https://images.tcdn.com.br/img/img_prod/728881/grade_ferro_fundido_bombe_curva_larga_sacada_varanda_80x24cm_6311_3_d48d2b3d72edeee2ff865c6b4b94681f.jpg | https://cdn.leroymerlin.com.br/products/grade_ferro_fundido_bombe_curva_larga_sacada_varanda_80x24cm_1567880827_ea43_600x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1686,7 +1750,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://fundicaoalfa.com.br/wp-content/uploads/2026/01/1-1.png | https://http2.mlstatic.com/D_NQ_NP_918444-MLB82585070625_022025-O.webp | https://a-static.mlcdn.com.br/420x420/grade-ferro-fundido-bombe-reta-sacada-varanda-escada-80x24cm-uniclaudio/plastificar2/6315p/b542a7efbad4453ab375123a6d44bcb5.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1734,7 +1802,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_espanhola_em_ferro_fundido_1538_1_b1cbc6fee977715509c936ef05e846ba.png | https://www.fundicaouniao.com.br/produtos/57b8_prod.jpg | https://images.tcdn.com.br/img/img_prod/148301/grade_janela_aco_forjado_1_46_x_1_66_90645_1_736a3265897e05127d15752bbad286bf.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1782,7 +1854,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/728881/grade_ferro_fundido_estrelinha_sacada_varanda_escada_50x37cm_6319_2_d134a3faaedbaa7c5356401de44b1ccd.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1830,7 +1906,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_857170-MLB53701084269_022023-O.webp | https://images.tcdn.com.br/img/img_prod/728881/grade_de_ferro_fundido_flor_de_lirio_curva_varanda_80x18cm_6285_3_cfeaca97b1bbaeb6cde8e769247fb51e.jpg | https://images.tcdn.com.br/img/img_prod/148301/grade_flor_lirio_curva_em_ferro_fundido_1541_1_8fbd11b9ce902b06bd14a2d85f61ba81.png</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1878,7 +1958,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_980705-MLB85613955364_062025-O-grade-ferro-fundido-flor-de-lirio-escada-pra-varanda-84x18cm.webp | https://http2.mlstatic.com/D_NQ_NP_857170-MLB53701084269_022023-O.webp | https://images.tcdn.com.br/img/img_prod/728881/grade_de_ferro_fundido_flor_de_lirio_curva_varanda_80x18cm_6285_3_cfeaca97b1bbaeb6cde8e769247fb51e.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1926,7 +2010,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>http://dcdn.mitiendanube.com/stores/002/503/307/products/grade-flor-de-lirio-reta-f2fce2c6d38db28fae17123412722347-640-0.jpg | https://lojawebcontinental.vtexassets.com/arquivos/ids/73272555-800-auto?v=639150655316770000&amp;width=800&amp;height=auto&amp;aspect=true | https://lojawebcontinental.vtexassets.com/arquivos/ids/73272585/MKP003986011589-3.jpg?v=639150655322870000</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1974,7 +2062,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://i.pinimg.com/736x/cc/ae/48/ccae487c48e631d0012648b8f7b71551.jpg | https://www.fundicaouniao.com.br/produtos/97ec_prod.jpg | https://cdn.leroymerlin.com.br/products/grade_ferro_fundido_flor_de_liz_bola_sacada_varanda_15x92cm_1567880804_7a18_600x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2022,7 +2114,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_789938-MLB85920124465_062025-O-grade-de-ferro-fundido-flor-de-liz-2-graus-varanda-87x14cm.webp | https://images.tcdn.com.br/img/img_prod/728881/grade_de_ferro_fundido_flor_de_liz_2_graus_varanda_87x14cm_6291_3_938bb74ff0fdfdd6c2619a8787b17998.jpg | https://images.tcdn.com.br/img/img_prod/728881/grade_de_ferro_fundido_flor_de_liz_2_graus_varanda_87x14cm_6291_2_c8a0dee87da9386e11fbcf73ee3dfbaf.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2072,7 +2168,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://carrefourbr.vtexassets.com/arquivos/ids/103112201-848-848/56b6916f6cf64290b3a7af3434a2a5b2.jpg?v=638128411829000000 | https://images.tcdn.com.br/img/img_prod/148301/grade_flor_liz_inclinada_em_ferro_fundido_1547_2_eb5ad11c8427db9e441ad9e70d6d13c9.jpg</t>
+          <t>https://carrefourbr.vtexassets.com/arquivos/ids/103112201-848-848/56b6916f6cf64290b3a7af3434a2a5b2.jpg?v=638128411829000000 | https://images.tcdn.com.br/img/img_prod/148301/grade_flor_liz_inclinada_em_ferro_fundido_1547_2_eb5ad11c8427db9e441ad9e70d6d13c9.jpg | https://down-br.img.susercontent.com/file/sg-11134201-7rffl-m30p2vvnmtvtb5 | https://fundicaoalfa.com.br/wp-content/uploads/2026/01/01-20.png | https://images.tcdn.com.br/img/img_prod/728881/grade_ferro_fundido_flor_de_liz_inclinada_varanda_86x15cm_6325_3_3a0e04c23cb8be3868d7fdb33ba089d0.jpg</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2218,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_650253-MLB80762928486_112024-O.webp | https://images.tcdn.com.br/img/img_prod/728881/grade_ferro_fundido_flor_de_liz_mini_varanda_sacada_58x13cm_6327_1_cb140eac50d034692dcdc6b3776961d1.jpg | https://http2.mlstatic.com/D_NQ_NP_741941-MLB82585080397_022025-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2270,7 +2370,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://cdn.leroymerlin.com.br/products/grade_ferro_fundido_imperial_1_grau_varanda_sacada_87x15_5cm_1567880817_2213_600x600.jpg | https://http2.mlstatic.com/D_NQ_NP_865344-MLB82584941621_022025-O-grade-ferro-fundido-imperial-1-grau-varanda-sacada-87x155cm.webp | https://fundicaoalfa.com.br/wp-content/uploads/2026/01/01-38.png</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2318,7 +2422,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_imperial_c_02_graus_em_ferro_fundido_1555_1_af042862bb590ce07ab0839594e6f339.png | https://images.tcdn.com.br/img/img_prod/148301/grade_imperial_c_02_graus_em_ferro_fundido_1555_2_5e4d9cc2ceafa9b2611a38a9c7e6b91a.png | https://images.tcdn.com.br/img/img_prod/728881/grade_ferro_fundido_imperial_2_grau_varanda_sacada_85x16cm_16149_3_a6cb900c82444202cd448595fbdf46eb.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2366,7 +2474,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://fundifercabofrio.com.br/wp-content/uploads/2023/09/imperial.jpg | https://http2.mlstatic.com/D_NQ_NP_626186-MLB53727139822_022023-O.webp | https://http2.mlstatic.com/D_NQ_NP_788810-MLB82584991255_022025-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2414,7 +2526,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://d5gag3xtge2og.cloudfront.net/producao/33580712/G/file_ef11bedd889615f5709f7e270dbbcf51.webp | https://dcdn-us.mitiendanube.com/stores/002/503/307/products/grade-imperial-pequena-09e18e1acdfe4ef9a517123177083173-480-0.webp | https://product-hub-prd.madeiramadeira.com.br/2857654/images/4af1ee58-c3c8-47d5-91ef-9b3dffcfe28737374796gradeferrofundidoimperialpequenavarandasacada49x15cmsku388328251600x450.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2462,7 +2578,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_650165-MLB71121276509_082023-O.webp | https://http2.mlstatic.com/D_NQ_NP_638288-MLB79909820131_102024-O.webp | https://fundbem.com.br/wp-content/uploads/2021/11/Grade-Imperial-Reta.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2512,7 +2632,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://images.tcdn.com.br/img/img_prod/1108186/1697553826_logotipo-da-loja-1.png | https://cdn.awsli.com.br/1030/1030675/produto/344137329/55e23c9dc5f24e6c792a6506becc8907-9dldusb1uu.jpg | https://http2.mlstatic.com/D_Q_NP_2X_727348-MLB110174449730_042026-P.webp</t>
+          <t>https://images.tcdn.com.br/img/img_prod/1108186/1697553826_logotipo-da-loja-1.png | https://cdn.awsli.com.br/1030/1030675/produto/344137329/55e23c9dc5f24e6c792a6506becc8907-9dldusb1uu.jpg | https://http2.mlstatic.com/D_Q_NP_2X_727348-MLB110174449730_042026-P.webp | https://imgv2-2-f.scribdassets.com/img/document/669592451/original/d69e8ba141/1?v=1 | https://images.tcdn.com.br/img/img_prod/697864/kit_com_02_pecas_garra_jacare_66_vermelha_26139_2_8ff22b0b4b0e83c47f300df1b443875d.jpeg | https://images.tcdn.com.br/img/img_prod/1202896/180_garra_tipo_jacare_p_bateria_100a_preto_075_6052_22534_1_306969ff60f2fbdb332fbeb683efd6c4.jpg</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2684,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_em_ferro_fundido_1571_2_4d9fa8daaca9fb91bb740102a4c3bb73.png | https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_em_ferro_fundido_1571_1_8888ee5312d9569bc4c747d453ab705a.png</t>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_em_ferro_fundido_1571_2_4d9fa8daaca9fb91bb740102a4c3bb73.png | https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_em_ferro_fundido_1571_1_8888ee5312d9569bc4c747d453ab705a.png | https://http2.mlstatic.com/D_NQ_NP_924716-MLB82585090287_022025-O.webp | https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_com_1_grau_em_ferro_fundido_1570_1_657a55950c9aec2de30ac114a7077dd3.png | https://d5gag3xtge2og.cloudfront.net/producao/33580702/G/file_178e08b0f61d462f9448db4585237852.webp</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2736,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_com_1_grau_em_ferro_fundido_1570_1_657a55950c9aec2de30ac114a7077dd3.png | https://d5gag3xtge2og.cloudfront.net/producao/33580712/M/grade-imperial-pequena-16x50.webp</t>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_com_1_grau_em_ferro_fundido_1570_1_657a55950c9aec2de30ac114a7077dd3.png | https://d5gag3xtge2og.cloudfront.net/producao/33580712/M/grade-imperial-pequena-16x50.webp | https://http2.mlstatic.com/D_NQ_NP_924716-MLB82585090287_022025-O.webp | https://images.tcdn.com.br/img/img_prod/728881/grade_ferro_fundido_ouro_preto_1_grau_sacada_varanda_86x15cm_6341_1_f9cf37db1c187fb0d2f846a01abdd0b5.jpg</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2788,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://cdn.leroymerlin.com.br/products/grade_ferro_fundido_ouro_preto_2_grau_sacada_escada_101x15cm_1567880811_5be1_600x600.jpg | https://cdn.leroymerlin.com.br/products/grade_ferro_fundido_ouro_preto_2_grau_sacada_escada_101x15cm_1567880811_4c5f_600x600.jpg | https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_em_ferro_fundido_1571_1_8888ee5312d9569bc4c747d453ab705a.png</t>
+          <t>https://cdn.leroymerlin.com.br/products/grade_ferro_fundido_ouro_preto_2_grau_sacada_escada_101x15cm_1567880811_5be1_600x600.jpg | https://cdn.leroymerlin.com.br/products/grade_ferro_fundido_ouro_preto_2_grau_sacada_escada_101x15cm_1567880811_4c5f_600x600.jpg | https://images.tcdn.com.br/img/img_prod/148301/grade_ouro_preto_em_ferro_fundido_1571_1_8888ee5312d9569bc4c747d453ab705a.png | https://images.tcdn.com.br/img/img_prod/728881/grade_ferro_fundido_ouro_preto_2_grau_sacada_escada_101x15cm_6343_3_b8daafcf7db56bdfd90f5e3e3c2b219d.jpg | https://images.tcdn.com.br/img/img_prod/728881/grade_ferro_fundido_ouro_preto_2_grau_sacada_escada_101x15cm_6343_1_c3a7cf0662b15f3a31f749dd8c9bceba.jpg | https://lojawebcontinental.vtexassets.com/arquivos/ids/73272540-800-auto?v=639150655313370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2840,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://dcdn-us.mitiendanube.com/stores/002/503/307/products/arte-para-produtos-9e1852a12cc51e50a517186442082954-1024-1024.webp | http://dcdn-us.mitiendanube.com/stores/002/503/307/products/grade-parreira-uva-reta-406a64cb1956204e3317123426610551-640-0.webp | https://images.tcdn.com.br/img/img_prod/148301/180_grade_parreira_uva_em_ferro_fundido_1574_2_9511bcd135da178ab31c74cb646a0e92.png</t>
+          <t>https://dcdn-us.mitiendanube.com/stores/002/503/307/products/arte-para-produtos-9e1852a12cc51e50a517186442082954-1024-1024.webp | http://dcdn-us.mitiendanube.com/stores/002/503/307/products/grade-parreira-uva-reta-406a64cb1956204e3317123426610551-640-0.webp | https://images.tcdn.com.br/img/img_prod/148301/180_grade_parreira_uva_em_ferro_fundido_1574_2_9511bcd135da178ab31c74cb646a0e92.png | https://i.pinimg.com/736x/19/a1/fe/19a1feb297765ecb424005092fd0c102.jpg | https://mondiniplantas.cdn.magazord.com.br/img/2025/04/produto/6460/pe-de-uva-isabel.jpg | https://images.tcdn.com.br/img/img_prod/148301/grade_parreira_uva_em_ferro_fundido_1574_1_4fd12f263a130b51c86e2b4a51d23387.png</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2890,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://tampaoegrelhagk.com.br/cdn/shop/files/Grade-de-Ferro-Fundido-Portuguesa-32X73-cm.webp?v=1774618806&amp;width=460 | https://d5gag3xtge2og.cloudfront.net/producao/33675908/G/2_sem_titulo.png | https://http2.mlstatic.com/D_NQ_NP_992706-MLB88738556124_082025-O-grade-ferro-fundido-portuguesa-sacada-varanda-escada-72x32cm.webp</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2818,7 +2942,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://product-hub-prd.madeiramadeira.com.br/744922540/images/d537c896-676c-46dc-acfb-e0cecb41b555889e42c6standardresolution.jpg | https://product-hub-prd.madeiramadeira.com.br/744922540/images/49d5f947-7b04-41aa-a6e8-e5a888552d1a7d3c1158standardresolution.jpg | https://images.tcdn.com.br/img/img_prod/728881/grade_de_ferro_fundido_ramada_sacada_varanda_escada_95x36cm_6301_1_f333f78db3be99deadac856b6b81f720.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2866,7 +2994,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/grade_ramada_estreita_em_ferro_fundido_1577_2_9eebd09db21da6112483cb5910bf77d4.jpg | https://d5gag3xtge2og.cloudfront.net/producao/33580696/G/grade-ramada-estreita-20x80.webp | https://i.pinimg.com/736x/2b/88/3d/2b883dc7d16a0a06a60bb16f4408aa56.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2914,7 +3046,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://fundicaoalfa.com.br/wp-content/uploads/2026/01/01-29.png | https://www.fundicaouniao.com.br/produtos/5c8b_prod.jpg | https://i.pinimg.com/originals/11/49/6e/11496eb32fd729f303945c08e14905bb.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2962,7 +3098,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/728881/grade_ferro_fundido_ramadinha_sacada_varanda_escada_45x33cm_6351_3_d0acca58d5a3690baa3bc5dce4e7fe89.jpg | https://i.pinimg.com/736x/e9/55/89/e955893263ebec395c315d485a75cb17.jpg | https://product-hub-prd.madeiramadeira.com.br/744922540/images/49d5f947-7b04-41aa-a6e8-e5a888552d1a7d3c1158standardresolution.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3010,7 +3150,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_995479-MLB82585120155_022025-O.webp | https://imagens.mfrural.com.br/mfrural-produtos-us/111534-442286-2335512-grade-roma-crsg-18x28x27-5.jpg | https://fameth.com.br/wp-content/uploads/2025/06/33.png</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3056,7 +3200,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://m.magazineluiza.com.br/a-static/420x420/prosacea-creme-facial-rosacea-21-25g/h2cshop/123p/a44fc1d34ea514ffd5b0ac51e913cc49.jpg | https://mc-df05ef79-e68e-4c65-8ea2-953494-cdn-endpoint.azureedge.net/-/media/gdm/us-branded/finacea/consumer/finacea-product-grey.jpg?rev=9d50e20b45204ed5a5155ef9722f637d | https://www.farmaciaeficacia.com.br/media/catalog/product/cache/33412c801b30787ffde781956b410354/c/r/creme-para-rosacea.jpg</t>
+          <t>https://m.magazineluiza.com.br/a-static/420x420/prosacea-creme-facial-rosacea-21-25g/h2cshop/123p/a44fc1d34ea514ffd5b0ac51e913cc49.jpg | https://mc-df05ef79-e68e-4c65-8ea2-953494-cdn-endpoint.azureedge.net/-/media/gdm/us-branded/finacea/consumer/finacea-product-grey.jpg?rev=9d50e20b45204ed5a5155ef9722f637d | https://www.farmaciaeficacia.com.br/media/catalog/product/cache/33412c801b30787ffde781956b410354/c/r/creme-para-rosacea.jpg | https://midias.agazeta.com.br/2025/04/17/produtos-para-rosacea-2694873-article.webp | https://cdn.awsli.com.br/2500x2500/1336/1336280/produto/292380951/prosacea--rosacea-gel-rfimportadoscwb-psjje068cz.jpg | https://m.media-amazon.com/images/I/710sWWRHQ1L._SL1000_.jpg</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3250,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/761023/flor_artificial_haste_de_copo_de_leite_ou_boca_de_jarro_70_cm_em_silicone_909_2_63218cad11e4bc140615fec87f5ad391.jpg | https://fundicaoalfa.com.br/wp-content/uploads/2026/01/01-14.png | https://images.tcdn.com.br/img/img_prod/1368629/copo_de_leite_com_folha_artificial_73_7_d23a5e7e885d24b03592ead6a62f9960.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3154,7 +3302,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://acdn.mitiendanube.com/stores/001/265/124/products/ponta-de-lanca-em-ferro-grade-portao-meia-polegada-medidas1-2184ff2c357432ff9316760576673060-1024-1024.jpg | https://acdn.mitiendanube.com/stores/001/265/124/products/ponta-de-lanca-jpg21-2d72f0e564a08dd8d816760576043260-1024-1024.jpg | https://carrefourbr.vtexassets.com/arquivos/ids/149701453/b55fbb62f749459f8b51f82547c74a59.jpg?v=638521279305870000</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3202,7 +3354,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/S/aplus-media-library-service-media/4d425376-a960-4dee-94ab-be1b462356b6.__CR0,0,970,600_PT0_SX970_V1___.jpg | https://img.ricardostatic.ch/images/3925a9ec-e4a6-4906-85f0-a2ff51c1884b/t_1000x750/flexa-classic-absturzsicherung-12 | https://www.nordicnest.kr/assets/blobs/flexa-3-in-1-cream/630997-01_1_Productimagemain-be9f894682.png?preset=tiny&amp;dpr=2</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3250,7 +3406,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_688987-MLB46192479663_052021-F.jpg | http://coferpon.com.br/wp-content/uploads/2016/12/Foto_Cod_1214201050142PM.jpg | https://down-br.img.susercontent.com/file/sg-11134201-7rbmz-m5cunousrzpc83</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3298,7 +3458,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://cloudflare.lipscosme.com/image/1d668d1709822717df9ee1f7-1662545889.png?auto=avif,webp&amp;fio=1&amp;orient=1&amp;width=1200 | https://www.medieval.pt/17307-large_default/lanca-grega-funcional.jpg | https://www.medieval.pt/17309-medium_default/lanca-grega-funcional.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3346,7 +3510,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/2ef2871135bcf066ec60f4772d36a0a1 | https://cdn.awsli.com.br/800x800/18/18325/produto/359278621/lan-a-imperial-40-00-gl4jih2siu.png | https://cdn.leroymerlin.com.br/products/ponteira_ponta_de_lanca_ferro_n31_grade_portao_muro_12cm_1570677993_d5a2_300x300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3448,7 +3616,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://carrefourbr.vtexassets.com/arquivos/ids/215018315-848-848/image-0.jpg?v=639154956550700000 | https://carrefourbr.vtexassets.com/arquivos/ids/215018319-848-848/image-1.jpg?v=639154956552600000 | https://carrefourbr.vtexassets.com/arquivos/ids/215018324-848-848/image-2.jpg?v=639154956554930000</t>
+          <t>https://carrefourbr.vtexassets.com/arquivos/ids/215018315-848-848/image-0.jpg?v=639154956550700000 | https://carrefourbr.vtexassets.com/arquivos/ids/215018319-848-848/image-1.jpg?v=639154956552600000 | https://carrefourbr.vtexassets.com/arquivos/ids/215018324-848-848/image-2.jpg?v=639154956554930000 | https://images.tcdn.com.br/img/img_prod/148301/pe_de_banco_frances_infantil_em_ferro_fundido_par_1740_1_7141a8624ea4ae79daf2ea080b439407.png | http://acdn-us.mitiendanube.com/stores/846/746/products/pe-de-banco-liso-infantil1-cf2fdac518228c38a616678475264737-640-0.jpg | https://alumiartmoveis.com.br/wp-content/uploads/2023/07/Frances-Infantil-2.png</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3720,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://images.tcdn.com.br/img/img_prod/148301/pinha_no_18_torcida_em_ferro_fundido_90365_2_2c4c2442f722f903f3aead2f6d43e971.png | https://images.tcdn.com.br/img/img_prod/148301/pinha_no_17_em_ferro_fundido_51194_1_416ec7dcd64fbca8b49bd41541346d11.png</t>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/pinha_no_18_torcida_em_ferro_fundido_90365_2_2c4c2442f722f903f3aead2f6d43e971.png | https://images.tcdn.com.br/img/img_prod/148301/pinha_no_17_em_ferro_fundido_51194_1_416ec7dcd64fbca8b49bd41541346d11.png | https://cdn.leroymerlin.com.br/products/pinha_ferro_fundido_n09_p__grade_portao_sacada_muro_8x18cm_1571960302_53af_600x600.jpg | https://d5gag3xtge2og.cloudfront.net/producao/33580568/G/file_cc92cf125f61699247c7091c59e13c87.webp | https://www.fundicaouniao.com.br/produtos/cee6_prod.jpg</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3770,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.aceramica.com.br/uploads/images/2024/04/410-pinha-m-25x15-410-1713986618.png | https://www.quintadellarte.com.br/quintadellarte/fotos/Pinha-decorativa-com-base-65cm-em-ferro-fundido-vrf163-para-jardins-e-projetos-classicos-__GP793438211.jpg | https://cdn.sanitop.pt/360/372889.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3652,7 +3824,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://images.tcdn.com.br/img/img_prod/148301/pinha_no_02_macica_em_ferro_fundido_1775_1_608ca08180d2ae0a60e27711cb62da9e.png | https://images.tcdn.com.br/img/img_prod/148301/90_pinha_no_03_soldada_em_ferro_fundido_1769_2_53f51b43c2a2ec9900bc6cb356e3bbbb.png</t>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/pinha_no_02_macica_em_ferro_fundido_1775_1_608ca08180d2ae0a60e27711cb62da9e.png | https://images.tcdn.com.br/img/img_prod/148301/90_pinha_no_03_soldada_em_ferro_fundido_1769_2_53f51b43c2a2ec9900bc6cb356e3bbbb.png | https://http2.mlstatic.com/D_NQ_NP_838720-MLB85920146971_062025-O.webp | https://img.elo7.com.br/product/zoom/573C4BF/pinha-31cm.jpg | https://www.fundicaouniao.com.br/produtos/6d0b_prod.jpg</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3876,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://acdn-us.mitiendanube.com/stores/001/272/619/products/imagem-do-whatsapp-de-2025-07-29-as-15-03-50_41ff47c1-94526cd20b9e186c8417538123802836-1024-1024.webp?utm_source=organic&amp;utm_campaign=&amp;utm_medium=&amp;utm_content=&amp;utm_term=&amp;subid=&amp;subid3=&amp;subid4=&amp;subid5=&amp;xcod=&amp;sck= | https://cdn.dooca.store/1056/products/1-pinha.jpg?v=1725038173 | https://images.tcdn.com.br/img/img_prod/148301/pinha_no_01_macica_em_ferro_fundido_1766_2_e57f162fda65bd2e4d513b886f48f704.png</t>
+          <t>https://acdn-us.mitiendanube.com/stores/001/272/619/products/imagem-do-whatsapp-de-2025-07-29-as-15-03-50_41ff47c1-94526cd20b9e186c8417538123802836-1024-1024.webp?utm_source=organic&amp;utm_campaign=&amp;utm_medium=&amp;utm_content=&amp;utm_term=&amp;subid=&amp;subid3=&amp;subid4=&amp;subid5=&amp;xcod=&amp;sck= | https://cdn.dooca.store/1056/products/1-pinha.jpg?v=1725038173 | https://images.tcdn.com.br/img/img_prod/148301/pinha_no_01_macica_em_ferro_fundido_1766_2_e57f162fda65bd2e4d513b886f48f704.png | https://images.tcdn.com.br/img/img_prod/728881/pinha_ferro_fundido_n10_p_grade_portao_sacada_muro_13x36cm_10195_3_071ab1c5b888c2f3c35866009bba531d.jpg | https://img.elo7.com.br/product/zoom/38666AE/pinha-grande-36cm-de-altura-e-20cm-largura-pi-1289.jpg | https://img.elo7.com.br/product/main/38666D8/pinha-grande-36cm-de-altura-e-20cm-largura-pi-1289.jpg</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3922,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.fundicaouniao.com.br/produtos/8e38_prod.jpg | https://http2.mlstatic.com/D_NQ_NP_720872-MLB89942400859_082025-O.webp | https://img.elo7.com.br/product/685x685/5251E56/pinha-natural-9-a-11-cm-cm-kit-com-40-pecas-pinha.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3798,7 +3974,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://lojawebcontinental.vtexassets.com/arquivos/ids/28821078/MKP003387000169-1.jpg?v=638313435155500000 | https://product-hub-prd.madeiramadeira.com.br/4351736/images/9a5b8acd-416c-4ae9-844d-c8c9c22b0e6e46759128pinhaabacaxicombaseferrofundidoprontoartes1sku48244198v12996832449x600.jpg | https://product-hub-prd.madeiramadeira.com.br/4351738/images/b7afc87b-e839-49cd-939f-8400a1d90e4d90758637pinhaabacaxicombaseferrofundidoprontoartes2sku48244198v13196831600x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3842,7 +4022,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/rosacea_flor_de_lirio_1917_2_f395010063b4dbceabb6c04c498a39c3.png | https://www.fundicaouniao.com.br/produtos/e777_prod.jpg | https://images.tcdn.com.br/img/img_prod/148301/rosacea_flor_de_lirio_1917_1_512f60373979ea577f2a4c241cdd0254.png</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3890,7 +4074,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>http://tampaoegrelhagk.com.br/cdn/shop/files/Rosacea-Flor-Liz-em-Ferro-Fundido-14-cm_1200x1200.webp?v=1774616916 | https://www.fundicaouniao.com.br/produtos/2592_prod.jpg | https://tampaoegrelhagk.com.br/cdn/shop/files/Rosacea-Flor-Liz-em-Ferro-Fundido-14-cm-2_1024x1024.webp?v=1774616923</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3918,7 +4106,11 @@
           <t>P.E.</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>FF ROSACEA IMPERIAL 10 CM, um produto de fundição com design floral.</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
@@ -3930,7 +4122,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/148301/rosacea_imperial_1919_1_b406cbbbf299b442123a6257651443ba.png | https://www.fundicaouniao.com.br/produtos/06cb_prod.jpg | https://fundicaoalfa.com.br/wp-content/uploads/2026/01/01-4.png</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4018,7 +4214,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_749372-MLB80538220823_112024-O.webp | https://img.irroba.com.br/filters:fill(transparent):quality(80)/panelasf/catalog/design-sem-nome-48.png | https://img.irroba.com.br/filters:format(webp):fill(transparent):quality(80)/panelasf/catalog/rosa-removebg-preview-1.png</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4062,7 +4262,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.fundicaouniao.com.br/produtos/06cb_prod.jpg | https://images.tcdn.com.br/img/img_prod/148301/rosacea_imperial_1919_1_b406cbbbf299b442123a6257651443ba.png | https://storage.googleapis.com/compras-production-xetrgvmk-production-compras-do-meu-jeito/public/content/product_images/6012532347328.webp</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4110,7 +4314,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://storage.googleapis.com/compras-production-xetrgvmk-production-compras-do-meu-jeito/public/content/product_images/6012507278213.webp | https://images.tcdn.com.br/img/img_prod/148301/1922_2_20200728112417.png | https://cdn.awsli.com.br/2500x2500/2680/2680531/produto/25965631819daa90ac2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4158,7 +4366,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1292607/fondue_vermelho_ferro_fundido_1_2_litros_16x10_cm_fumil_4645_2_0e525331b46986956152a978b0f00e2c.jpeg | https://images.tcdn.com.br/img/img_prod/728881/fondue_de_ferro_fundido_1_2_litros_16_cm_diametro_12061_1_56882b66bd05e7fcf468a7fd5e6c5dcd.jpg | https://images.tcdn.com.br/img/img_prod/763745/180_te_bolsa_e_flange_em_ferro_fundido_ductil_pn10_pn16_pn25_dn_50_a_1_200_6723_1_b5675381ef62a6952f49b0b4def28df7.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4206,7 +4418,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://imgv2-1-f.scribdassets.com/img/document/760435653/original/295672ce8e/1727472284?v=1 | https://blogger.googleusercontent.com/img/a/AVvXsEhI4ecS_zKVefmFHi_CzB04syaSw_zVJijNgCzniOp8hUEyg98EXfM68mVo57OQJFVEZ0czJkJpKQi1qnAVWilxsqYVVogJ3i5tsSwNT6cDXhftAgopBR8Z1EixV2rzzNdOOuNHT8PshMjpLs_VyP-hT7bbinWpc4S3b1zRiT9Oolq8EPH1frt57mUBHMbD | https://media.licdn.com/dms/image/v2/D4D22AQHBWIxTRzbgrQ/feedshare-shrink_1280/B4DZcNikOtG0Ao-/0/1748278855965?e=2147483647&amp;v=beta&amp;t=P1zFzwxXuniB_92vd7DfbCLm3ArtqqRnk0aYNZPG8w4</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4239,7 +4455,11 @@
           <t>Martelo rompedor Vonder MRV 1500, 220V.</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Potência: 1500W, Peso: 5kg, Tensão: 220V</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4250,7 +4470,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_858127-MLB75492958587_032024-O-martelete-rompedor-mpv-1500-5kg-220v-vonder.webp | https://lojaqueroquero.vtexassets.com/arquivos/ids/3194201-800-auto?v=638234819612970000&amp;width=800&amp;height=auto&amp;aspect=true | https://images.tcdn.com.br/img/img_prod/469103/martelete_perfurador_rompedor_5kg_1500w_mpv1500_220v_vonder_147809_1_01d0a4becda9e7ddbaf683e72d506fe4.png</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4283,7 +4507,11 @@
           <t>Parafuso para concreto PCE 12 100, utilizado em aplicações que exigem fixação em concreto.</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Diâmetro: 12mm, Comprimento: 100mm, Embalagem: 25 unidades</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -4294,7 +4522,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://i.pinimg.com/originals/9a/96/cc/9a96cc241088ce953da501de8139fa68.jpg | https://down-br.img.susercontent.com/file/sg-11134201-7rdwv-lxmo8h9o9y8664 | https://images.cws.digital/produtos/gg/62/90/parafuso-sextavado-para-concreto-12-x-100mm-embalagem-com-25-unidades-10959062-1770725955295.png</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4342,7 +4574,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_896250-MLB96083632450_102025-O-tela-alambrado-fio-12-malha-3-pvc-30m-x-120alt.webp | https://images.tcdn.com.br/img/img_prod/1200936/tela_alambrado_revestido_pvc_verde_m_76_20mm_fio_12_alt_2_00m_por_metro_861_1_534d3db6498d67e239b631b895504758.jpeg | https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_em_pvc_verde_tellacor_malha_de_12_x_12_mm_fio_de_0_90_mm_rolo_de_25_00_x_1_00_1789_2_40372811f320a7f58054e78e12c7c24f.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4390,7 +4626,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_12_revestido_pvc_verde_malha_50_rolo_20m_51_1_f6306acb9d9ee5be6ce53317f7ebf6bd.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_em_pvc_verde_tellacor_malha_de_12_x_12_mm_fio_de_0_90_mm_rolo_de_25_00_x_1_00_1789_2_40372811f320a7f58054e78e12c7c24f.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4438,7 +4678,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_12_revestido_pvc_verde_malha_50_rolo_20m_51_1_f6306acb9d9ee5be6ce53317f7ebf6bd.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_alambrado_revestido_pvc_verde_malha_2_fio_12_rolo_de_25x1_00m_801_1_534d3db6498d67e239b631b895504758.jpeg | http://dcdn-us.mitiendanube.com/stores/002/157/098/products/prancheta-191-850879a15150c4a43716662851181028-640-0.png</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4486,7 +4730,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>http://dcdn-us.mitiendanube.com/stores/002/157/098/products/prancheta-191-850879a15150c4a43716662851181028-640-0.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_em_pvc_verde_tellacor_malha_de_12_x_12_mm_fio_de_0_90_mm_rolo_de_25_00_x_1_00_1789_2_40372811f320a7f58054e78e12c7c24f.jpeg | https://www.southsafe.com.br/assets/img/produtos/tela-alambrado-losangular-malha-80mm-x-80mm-fio-12-revestida-pvc-verde-1688214394.JPG</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4534,7 +4782,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>http://dcdn-us.mitiendanube.com/stores/002/157/098/products/prancheta-191-850879a15150c4a43716662851181028-640-0.png | https://images.tcdn.com.br/img/img_prod/1337675/90_tela_alambrado_fio_12_revestido_pvc_verde_malha_75_rolo_20m_55_1_f5f768344113b2e5e4a05fd511579bed.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_em_pvc_verde_tellacor_malha_de_12_x_12_mm_fio_de_0_90_mm_rolo_de_25_00_x_1_00_1789_2_40372811f320a7f58054e78e12c7c24f.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4582,7 +4834,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://www.southsafe.com.br/assets/img/produtos/tela-alambrado-losangular-malha-80mm-x-80mm-fio-12-revestida-pvc-verde-1688214394.JPG | https://www.casadascercas.com.br/upload/produto/imagem/b_tela-revestida-em-pvc-verde-fio-12-380mm-malha-376cm-rolo-20m-66-1.webp | http://dcdn-us.mitiendanube.com/stores/002/157/098/products/prancheta-191-850879a15150c4a43716662851181028-640-0.png</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4678,7 +4934,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_revestido_pvc_verde_malha_70_rolo_25m_69_1_0d040b17641daf515125ebd923d2c86e.png | https://http2.mlstatic.com/D_NQ_NP_872404-MLB47092724188_082021-O.webp | https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_pvc_tellacor_azul_fio_2_50mm_rolo_de_1_00x25mts_malha_10x5cm_739_1_6cacebceb44921520e282316d22f9106.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4774,7 +5034,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_revestido_pvc_verde_malha_45_rolo_25m_65_1_62f960a1011f24a669bb8667d54dd392.png | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_residencial_fio_14_galvanizado_malh_1_20251217161057_3be4eb3bfef8.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_pvc_tellacor_azul_fio_2_50mm_rolo_de_1_00x25mts_malha_10x5cm_739_1_6cacebceb44921520e282316d22f9106.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4822,7 +5086,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tela_alambrado_revestido_pvc_verde_m_50_80mm_fio_14_1_00malt_por_metro_817_1_534d3db6498d67e239b631b895504758.jpeg | https://http2.mlstatic.com/D_NQ_NP_601880-MLB31122453534_062019-O.webp | https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_pvc_tellacor_azul_fio_2_50mm_rolo_de_1_00x25mts_malha_10x5cm_739_1_6cacebceb44921520e282316d22f9106.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4870,7 +5138,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_pvc_tellacor_azul_fio_2_50mm_rolo_de_1_00x25mts_malha_10x5cm_739_1_6cacebceb44921520e282316d22f9106.jpeg | https://images.tcdn.com.br/img/img_prod/1337675/kit_tela_alambrado_fio_14_revestido_pvc_verde_malha_70_4_arames_p_esticar_telas_fio_12_1_arame_p_ama_175_1_d89c77a78524d748d3c61ce14a4ab69a.png | https://images.tcdn.com.br/img/img_prod/1337675/kit_tela_alambrado_fio_14_revestido_pvc_verde_malha_70_4_arames_p_esticar_telas_fio_12_1_arame_p_ama_175_1_a0150a087cf2f656e240c291637a8d26.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5014,7 +5286,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://www.casadascercas.com.br/upload/produto/imagem/b_tela-alambrado-fio-16-pvc-230mm-malha-25cm-rolo-20m-282-1.webp | https://http2.mlstatic.com/D_NQ_NP_763934-MLB76067599770_052024-O.webp | https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_pvc_tellacor_azul_fio_2_50mm_rolo_de_1_00x25mts_malha_10x5cm_739_1_6cacebceb44921520e282316d22f9106.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5062,7 +5338,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_16_revestido_pvc_verde_malha_25_rolo_25m_89_1_711eab610e81574b8bbe91803be4bff9.png | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_16_revestido_pvc_verde_malha_50_rolo_25m_93_1_39057a5bfeb4499c1e73e91326877747.png | https://http2.mlstatic.com/D_NQ_NP_916238-MLB84139059154_052025-O-tela-alambrado-pvc-fio-16-malha-5-altura-180-comprimento-25.webp</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5110,7 +5390,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://www.telasrhv.com.br/wp-content/uploads/2021/01/como-fazer-cerca-de-tela.jpg | https://www.casadascercas.com.br/upload/produto/imagem/b_tela-alambrado-fio-16-pvc-230mm-malha-25cm-rolo-20m-282-1.webp | https://http2.mlstatic.com/D_NQ_NP_858112-MLB81140768260_122024-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5158,7 +5442,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_16_revestido_pvc_verde_malha_40_rolo_25m_91_1_83e290d0ac9fbeb92fa0401f587e478e.png | https://images.tcdn.com.br/img/img_prod/1337675/kit_tela_alambrado_fio_16_malha_40_04_arames_p_esticar_telas_fio_12_01_arame_p_amarrar_fio_16_187_1_430976654b0b53aa0f34f4509f9ada73.png</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5206,7 +5494,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/180_tela_alambrado_fio_16_revestido_pvc_verde_malha_50_rolo_25m_93_1_39057a5bfeb4499c1e73e91326877747.png | https://images.tcdn.com.br/img/img_prod/1337675/kit_tela_alambrado_fio_16_malha_50_04_arame_p_esticar_telas_fio_12_01_arame_p_amarrar_fio_16_189_1_d064d7276c73043c3fceeaa7b2dce8d8.png | https://images.tcdn.com.br/img/img_prod/1337675/kit_tela_alambrado_fio_16_malha_50_04_arame_p_esticar_telas_fio_12_01_arame_p_amarrar_fio_16_177_1_53ebdab308c7d242bf31cef52f6e978b.png</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5254,7 +5546,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://product-hub-prd.madeiramadeira.com.br/598697701/images/842e0773-c9ba-4901-8508-f82d1274176eio16165mmmalha5x5cmrolo25m.jpg | https://http2.mlstatic.com/D_NQ_NP_939623-MLB87579670901_072025-O.webp | https://www.telasrhv.com.br/wp-content/uploads/2021/01/como-fazer-cerca-de-tela.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5302,7 +5598,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_970222-MLB80621057466_112024-O-tela-alambrado-pvc-fio-16-malha-7-altura-100-comprimento-25.webp | https://images.tcdn.com.br/img/img_prod/1337675/kit_tela_alambrado_fio_16_malha_70_arame_p_esticar_telas_fio_12_arame_p_amarrar_fio_16_191_1_4670f4be05cb18ef91cc9c015787b782.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_soldada_revestida_pvc_tellacor_azul_fio_2_50mm_rolo_de_1_00x25mts_malha_10x5cm_739_1_6cacebceb44921520e282316d22f9106.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5350,7 +5650,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_10_galvanizado_malha_50_rolo_20m_25_1_6ca21e0dd6a34b67edee8ca58477ce31.jpg | https://images.tcdn.com.br/img/img_prod/1337675/90_tela_alambrado_fio_10_galvanizado_malha_75_rolo_20m_29_1_88e9bc995c74e694612ec066355f5b2e.png | https://images.tcdn.com.br/img/img_prod/1337675/90_tela_alambrado_fio_12_galvanizado_malha_50_acabamento_farpado_rolo_20m_39_1_5ba22bb0109e156ad3dded626277afff.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5398,7 +5702,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>https://global.cdn.magazord.com.br/comercialklock/img/2023/08/produto/1264/design-sem-nome-26.png | https://global.cdn.magazord.com.br/hiperfer/img/2024/04/produto/14504/01-tela-soldada-galvanizada-malha-5-x-10-cm-fio-1-65-mm-altura-1-00-m-rolo-com-25-m-franz.jpeg | https://acomanaus.com.br/wp-content/uploads/2024/09/tela_ondulada_malha_1_fio_12_galvanizada_1_00m_alt_21_1_4e4feb202c8c57ac4d04b1b536e3499d.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5446,7 +5754,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/90_tela_alambrado_fio_10_galvanizado_malha_75_rolo_20m_29_1_88e9bc995c74e694612ec066355f5b2e.png | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_10_galvanizado_malha_70_rolo_20m_27_1_8e7585c6c0daf51f9e0ca40616f792c2.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_3_4_fio_10_altura_1_50m_preco_por_metro_1867_2_7e06d53a3645dca7cf079c08cfbea746.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5494,7 +5806,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_galvanizada_para_empreendimentos_fio_12_259_1_3415185683d7340ad0e591617d5ec83c.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_19_05mm_fio_12_alt_1_00m_295_1_09c48e12e2c7c546315ec3ce10a00c68.jpg | https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_m_sob_medida_21_1_8ce9d6bb816205313290c0dbb32cd147.png</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5542,7 +5858,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_galvanizada_para_empreendimentos_fio_12_259_1_3415185683d7340ad0e591617d5ec83c.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_19_05mm_fio_12_alt_1_00m_295_1_09c48e12e2c7c546315ec3ce10a00c68.jpg | https://down-br.img.susercontent.com/file/b3738f90668a5830c0b8272388dbaed7</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5590,7 +5910,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_19_05mm_fio_12_alt_1_00m_295_1_09c48e12e2c7c546315ec3ce10a00c68.jpg | https://images.tcdn.com.br/img/img_prod/1337675/tela_galvanizada_para_empreendimentos_fio_12_259_1_3415185683d7340ad0e591617d5ec83c.png | https://images.tcdn.com.br/img/img_prod/1159212/tela_alambrado_1_80_alt_fio_12_malha_8_5_cm_rolo_25_metros_21_5_e5534821325ab267f283857131b35e87.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5638,7 +5962,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_12_galvanizado_malha_50_acabamento_liso_rolo_20m_31_1_4d212cd5fefc1e3ce46e1e058b8e07d2.jpg | https://images.tcdn.com.br/img/img_prod/1337675/180_tela_alambrado_fio_12_galvanizado_malha_50_acabame_1_20251229165105_9543eefcece0.png | https://images.tcdn.com.br/img/img_prod/1337675/tela_galvanizada_para_empreendimentos_fio_12_259_1_3415185683d7340ad0e591617d5ec83c.png</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5686,7 +6014,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_galvanizada_para_empreendimentos_fio_12_259_1_3415185683d7340ad0e591617d5ec83c.png | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_19_05mm_fio_12_alt_1_00m_295_1_09c48e12e2c7c546315ec3ce10a00c68.jpg | https://http2.mlstatic.com/D_NQ_NP_732058-MLB30367102639_052019-W.webp</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5734,7 +6066,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/kit_tela_alambrado_fio_12_malha_75_liso_3_arames_p_esticar_telas_fio_12_arame_p_amarrar_fio_16_165_1_3329564064e0d939b719c133cbd7d6d3.png | https://images.tcdn.com.br/img/img_prod/1337675/tela_galvanizada_para_empreendimentos_fio_12_259_1_3415185683d7340ad0e591617d5ec83c.png | https://kesdobrasil.com.br/wp-content/uploads/2025/10/20251030_102640-scaled.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5782,7 +6118,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_galvanizada_para_empreendimentos_fio_12_259_1_3415185683d7340ad0e591617d5ec83c.png | https://images.tcdn.com.br/img/img_prod/1159212/tela_alambrado_1_80_alt_fio_12_2_76_mm_malha_8_5_cm_rolo_25_1_319ab99612bb22226641c62c0f0add5d.jpg | https://images.tcdn.com.br/img/img_prod/1159212/tela_alambrado_1_80_alt_fio_12_malha_8_5_cm_rolo_25_metros_21_3_c46f9da4c4fd8a5901fa348f14a1f4b0.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5830,7 +6170,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_galvanizado_malha_80_rolo_25m_63_1_24172ed235ca09be435a93eb29bbc2d7.png | https://imagens.mfrural.com.br/mfrural-produtos-us/430840-662048-67869134-tela-otis-galvanizada-fio-2-10mm-bwg-14-m-.jpg | https://kesdobrasil.com.br/wp-content/uploads/2025/10/20251030_102328-scaled.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5878,7 +6222,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>https://cdn.diferpan.com.br/produtos/8935/8935.jpg | https://imagens.mfrural.com.br/mfrural-produtos-us/430840-662048-67869134-tela-otis-galvanizada-fio-2-10mm-bwg-14-m-.jpg | https://http2.mlstatic.com/D_NQ_NP_732155-MLB90556576420_082025-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5926,7 +6274,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_galvanizado_malha_40_rolo_25m_57_1_32aef2dabcd83df12b484f63d437b8c7.png | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_residencial_fio_14_galvanizado_malh_1_20260423113533_ceb875250bc2.png | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_galvanizado_malha_50_rolo_25m_59_1_4dad7bda1cdbefc96aa4aaf2b12f8629.png</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5974,7 +6326,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_galvanizado_malha_50_rolo_25m_59_1_51287a254250205c579526d41f9dfbef.jpg | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_galvanizado_malha_50_rolo_25m_59_1_4dad7bda1cdbefc96aa4aaf2b12f8629.png | https://imagens.mfrural.com.br/mfrural-produtos-us/430840-662048-67869134-tela-otis-galvanizada-fio-2-10mm-bwg-14-m-.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6070,7 +6426,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://a-static.mlcdn.com.br/undefinedxundefined/tela-alambrado-galvanizado-fio-14-malha-75mm-25m-x-10m-de-altura-ribertelas/ribertelasalambrados/e1dfad967a4a11ed93ce4201ac185019/de1f35417a7176455976288e3664f5fa.jpeg | https://imagens.mfrural.com.br/mfrural-produtos-us/430840-662048-67869134-tela-otis-galvanizada-fio-2-10mm-bwg-14-m-.jpg | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_galvanizado_malha_50_rolo_25m_59_1_4dad7bda1cdbefc96aa4aaf2b12f8629.png</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6214,7 +6574,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_644075-MLB47949982116_102021-O.webp | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_16_galvanizado_malha_80_rolo_25m_81_1_9edab3ddf24427a65e5e19d9046629e0.png | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_16_galvanizado_malha_25_rolo_25m_73_1_1af10772842815893d450a017bb833ca.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6262,7 +6626,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tecido_galvanizado_malha_16_fio_30_altura_de_1_00m_preco_por_metro_1673_2_2c43c85e3d0952e5a9fd46171e673be6.jpeg | https://http2.mlstatic.com/D_NQ_NP_868996-MLB46603451293_072021-O.webp | https://images.tcdn.com.br/img/img_prod/1200936/tecido_galvanizado_malha_16_fio_30_altura_de_1_00m_preco_por_metro_1673_1_3ea109b3c5d4020467c8290be2bd4324.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6742,7 +7110,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>http://valetelas.com.br/wp-content/uploads/2023/09/Tela-ondulada.webp | https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_1_00m_alt_21_1_4e4feb202c8c57ac4d04b1b536e3499d.jpeg | https://telasimperial.com.br/wp-content/uploads/2021/12/telas-onduladas-1-300x300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6790,7 +7162,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>http://valetelas.com.br/wp-content/uploads/2023/09/Tela-ondulada.webp | https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_1_00m_alt_21_1_4e4feb202c8c57ac4d04b1b536e3499d.jpeg | https://www.omegatelas.com.br/blog/wp-content/uploads/2023/12/tela-ondulada.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6838,7 +7214,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>http://valetelas.com.br/wp-content/uploads/2023/09/Tela-ondulada.webp | https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_1_00m_alt_21_1_4e4feb202c8c57ac4d04b1b536e3499d.jpeg | https://telasschramm.com.br/wp-content/uploads/2024/01/2.-Tela-Ondulada-min-scaled.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6886,7 +7266,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>http://valetelas.com.br/wp-content/uploads/2023/09/Tela-ondulada.webp | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_3_4_fio_10_altura_1_50m_preco_por_metro_1867_2_7e06d53a3645dca7cf079c08cfbea746.jpeg | https://telasimperial.com.br/wp-content/uploads/2021/12/telas-onduladas-1-300x300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6934,7 +7318,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>http://valetelas.com.br/wp-content/uploads/2023/09/Tela-ondulada.webp | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_3_4_fio_10_altura_1_50m_preco_por_metro_1867_2_7e06d53a3645dca7cf079c08cfbea746.jpeg | https://telasimperial.com.br/wp-content/uploads/2021/12/telas-onduladas-1-300x300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7030,7 +7418,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_812556-MLB89269293250_082025-O.webp | https://www.telashav.com.br/wp-content/uploads/2021/10/tela-corrugada-fio-12-malha-20mm-800x600.jpg | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_1_fio_12_alt_1_00m_227_1_09c48e12e2c7c546315ec3ce10a00c68.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7126,7 +7518,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_812556-MLB89269293250_082025-O.webp | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_1_fio_12_altura_2_00preco_por_metro_1555_1_fc59a20736ce774f3aa8e6d96bff32cc.jpg | https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_m_sob_medida_21_1_8ce9d6bb816205313290c0dbb32cd147.png</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7174,7 +7570,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://www.telashav.com.br/wp-content/uploads/2021/10/tela-quadriculada-fio12-malha-30mm-3.jpg | https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_m_sob_medida_21_1_8ce9d6bb816205313290c0dbb32cd147.png | https://www.telashav.com.br/wp-content/uploads/2021/10/tela-corrugada-fio-12-malha-20mm-800x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7222,7 +7622,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_m_sob_medida_21_1_8ce9d6bb816205313290c0dbb32cd147.png | https://catumbi.com.br/novo/image/cache/catalog/ondulada/novas-imagens/tela-ondulada-a-750x750.jpg | https://www.tecnofuro.com.br/uploads/pagina/elemento/campo/2023/05/fKkgdNNX716CLZeT/tela-ondulada-aco-inox-1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7270,7 +7674,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_1_fio_12_alt_1_00m_227_1_09c48e12e2c7c546315ec3ce10a00c68.jpg | https://http2.mlstatic.com/D_NQ_NP_732058-MLB30367102639_052019-O.webp | https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_m_sob_medida_21_1_8ce9d6bb816205313290c0dbb32cd147.png</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7318,7 +7726,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_25_40mm_fio_12_alt_1_00m_rolo_de_30_00m_1113_1_09c48e12e2c7c546315ec3ce10a00c68.jpg | https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_m_sob_medida_21_1_8ce9d6bb816205313290c0dbb32cd147.png | https://down-br.img.susercontent.com/file/sg-11134201-7rd4l-luxlj3vydt2h7b</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7366,7 +7778,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha1_2_fio_14_altura_2_0m_preco_por_metro_1783_2_7e06d53a3645dca7cf079c08cfbea746.jpeg | https://www.omegatelas.com.br/blog/wp-content/uploads/2023/12/tela-ondulada.jpg | https://http2.mlstatic.com/D_NQ_NP_840839-MLB91965379710_092025-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7414,7 +7830,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/180_tela_ondulada_galvanizada_malha_1_fio_14_altura_1_20m_preco_por_metro_1957_1_09c48e12e2c7c546315ec3ce10a00c68.jpeg | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_galvanizado_malha_50_rolo_25m_59_1_4dad7bda1cdbefc96aa4aaf2b12f8629.png | http://valetelas.com.br/wp-content/uploads/2023/09/Tela-ondulada.webp</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7462,7 +7882,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha1_2_fio_14_altura_2_0m_preco_por_metro_1783_2_7e06d53a3645dca7cf079c08cfbea746.jpeg | https://http2.mlstatic.com/D_NQ_NP_838892-MLB30367106638_052019-O.webp | https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_1_00m_alt_21_1_4e4feb202c8c57ac4d04b1b536e3499d.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7510,7 +7934,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_galvanizado_malha_50_rolo_25m_59_1_4dad7bda1cdbefc96aa4aaf2b12f8629.png | https://catumbi.com.br/novo/image/cache/catalog/ondulada/novas-imagens/tela-ondulada-b-750x750.jpg | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha1_2_fio_14_altura_2_0m_preco_por_metro_1783_4_d61e918c42b742e01d948fc202dc48cf.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7558,7 +7986,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_22_23mm_fio_14_alt_1_00m_297_1_09c48e12e2c7c546315ec3ce10a00c68.jpg | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha1_2_fio_14_altura_2_0m_preco_por_metro_1783_2_7e06d53a3645dca7cf079c08cfbea746.jpeg | https://images.tcdn.com.br/img/img_prod/1337675/tela_alambrado_fio_14_galvanizado_malha_50_rolo_25m_59_1_4dad7bda1cdbefc96aa4aaf2b12f8629.png</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7606,7 +8038,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_de_3_8_pol_fio_16_1_65mm_galvanizada_1_1_371b97772cee5463413584f7a0e6dead.jpeg | https://telasschramm.com.br/wp-content/uploads/2024/01/2.-Tela-Ondulada-min-scaled.jpg | http://valetelas.com.br/wp-content/uploads/2023/09/Tela-ondulada.webp</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7654,7 +8090,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_de_3_8_pol_fio_16_1_65mm_galvanizada_1_1_371b97772cee5463413584f7a0e6dead.jpeg | https://telasschramm.com.br/wp-content/uploads/2024/01/2.-Tela-Ondulada-min-scaled.jpg | https://www.telashav.com.br/wp-content/uploads/2021/10/tela-quadriculada-fio-12-malha-15mm.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7702,7 +8142,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_de_3_8_pol_fio_16_1_65mm_galvanizada_1_1_371b97772cee5463413584f7a0e6dead.jpeg | https://telasschramm.com.br/wp-content/uploads/2024/01/2.-Tela-Ondulada-min-scaled.jpg | https://www.telashav.com.br/wp-content/uploads/2021/10/tela-corrugada-fio-12-malha-20mm.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7750,7 +8194,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1085053/tela_ondulada_malha_1_fio_12_galvanizada_1_00m_alt_21_1_4e4feb202c8c57ac4d04b1b536e3499d.jpeg | https://http2.mlstatic.com/D_NQ_NP_945691-MLB89481090959_082025-O-tela-ondulada-galv-malha-723mm-3-fio-18-50cm-x-100cm.webp | https://www.telashav.com.br/wp-content/uploads/2021/10/tela-quadriculada-fio-12-malha-15mm-800x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7798,7 +8246,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_940669-MLB97564015067_112025-O-tela-ondulada-galv-malha-723mm-3-fio-18-500-x-100m.webp | https://primetelascwb.com.br/wp-content/uploads/elementor/thumbs/Tela-ondulada-Prime-Telas-Curitiba-2-1-qkhtfqrh5zqk0rbeacxwbt8xhcwel5inpgx41nwfr4.webp | https://www.omegatelas.com.br/blog/wp-content/uploads/2023/12/tela-ondulada.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7846,7 +8298,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha1_2_fio_14_altura_2_0m_preco_por_metro_1783_2_7e06d53a3645dca7cf079c08cfbea746.jpeg | https://www.omegatelas.com.br/blog/wp-content/uploads/2023/09/tela-ondulada.jpg | https://www.telashav.com.br/wp-content/uploads/2021/10/tela-corrugada-fio-12-malha-20mm-800x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7894,7 +8350,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://telasschramm.com.br/wp-content/uploads/2024/01/2.-Tela-Ondulada-min-scaled.jpg | https://http2.mlstatic.com/D_NQ_NP_897308-MLB91252698512_092025-O.webp | http://valetelas.com.br/wp-content/uploads/2023/09/Tela-ondulada.webp</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7942,7 +8402,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://yata-apix-0202bf75-58f7-48f1-8ea7-031e3122502e.s3-object.locaweb.com.br/50a00a2323414f298ac92a975fc941ca.jpg | https://www.omegatelas.com.br/blog/wp-content/uploads/2023/12/tela-ondulada.jpg | https://telasschramm.com.br/wp-content/uploads/2024/01/2.-Tela-Ondulada-min-768x513.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7990,7 +8454,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/b3738f90668a5830c0b8272388dbaed7 | https://telasschramm.com.br/wp-content/uploads/2024/01/2.-Tela-Ondulada-min-768x513.jpg | https://images.tcdn.com.br/img/img_prod/1200936/tela_ondulada_galvanizada_malha_112_40x40mm_fio_12_1_20250923163323_f4a926377f76.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8038,7 +8506,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://fabricapontual.com.br/wp-content/uploads/2023/08/telha-galvalume-branca.jpg | https://images.tcdn.com.br/img/img_prod/1318890/telha_pre_pintada_branca_tp40_0_43_metro_linear_3_65_20067_1_78034ec7a85ab7fec6745e85a489fb1a.jpg | https://madeireirasaojosels.com.br/cdn/shop/files/Telha-Branca_800x.jpg?v=1711631575</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8086,7 +8558,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://kbvaco.com.br/wp-content/uploads/2021/04/Telha-Galvalume-043-KBV-II.jpg | https://kbvaco.com.br/wp-content/uploads/2022/10/27.png | https://kbvaco.com.br/wp-content/uploads/2024/03/WhatsApp-Image-2025-08-25-at-16.56.59-1.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8134,7 +8610,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://img.olx.com.br/images/64/649686263674297.jpg | https://1ll.com.br/wp-content/uploads/2022/01/Telha-Galvalume-Sanduiche-Galvanizada-em-Matao-Araraquara-Sao-Carlos-Ribeirao-Preto-Catanduva-Jaboticabal-Itapolis-Tabatinga-Taquaritinga-Monte-Alto-SP-768x768.jpeg | https://product-hub-prd.madeiramadeira.com.br/981467/images/dc6dc99e-2bfb-48d3-8af0-46718f8581d1alalumino1742903926200zoom.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8178,7 +8658,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://fabricapontual.com.br/wp-content/uploads/2023/08/telha-galvalume-branca.jpg | https://www.fortedoserralheiro.com.br/2816-product_zoom/telha-trapezoidal-40980-galvalume-pintada-1-face.jpg | http://madeireirasaojosels.com.br/cdn/shop/files/Telha-Branca.jpg?v=1711631575</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8222,7 +8706,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://fabricapontual.com.br/wp-content/uploads/2023/08/telha-galvalume-branca.jpg | https://images.tcdn.com.br/img/img_prod/1318890/telha_pre_pintada_branca_tp40_0_43_metro_linear_3_65_20067_1_78034ec7a85ab7fec6745e85a489fb1a.jpg | https://www.fortedoserralheiro.com.br/2815-large_default/telha-trapezoidal-40980-galvalume-pintada-2-face.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8266,7 +8754,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://indoormaterial.com.br/wp-content/uploads/2024/09/telha-laranja-.jpg | https://www.institutodaconstrucao.com.br/wp-content/uploads/2024/01/Captura-de-tela-2024-01-31-101235.png | https://img.freepik.com/fotos-premium/telhado-pre-fabricado-de-telhas-laranja-em-construcao-de-casa-simples_41386-929.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8310,7 +8802,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>http://www.cotanet.com.br/img/site/produtos/telha-isotermica-isopor.jpg | https://www.termovale.com.br/imagens/subcategorias/566720db5bdaad5816cf157a2a458ec2.png | https://styroville.com.br/wp-content/uploads/2024/10/TELHA-1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8358,7 +8854,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>https://site.thermo-iso.com.br/wp-content/uploads/2024/12/TR_25-1020_EPS_VERDE.jpg | https://images.tcdn.com.br/img/img_prod/1348726/90_telha_sanduiche_termo_acustica_trapezoidal_colorida_1_face_branca_preenchimento_isopor_256723624_1_ee28a9185597a0ffcd9f26a89939b4f9.jpg | https://pontescm.com.br/wp-content/uploads/2025/09/cores-disponiveis-1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8406,7 +8906,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1348726/telha_sanduiche_termo_acustica_trapezoidal_colorida_2_faces_preenchimento_isopor_256707237_5_5026102167ecc21f940c7f0e95b6207a.png | https://images.tcdn.com.br/img/img_prod/1348726/telha_sanduiche_termo_acustica_trapezoidal_colorida_2_faces_preenchimento_isopor_256707237_4_526510fad9b9883b7e9477d8cb2f9040.png | https://images.tcdn.com.br/img/img_prod/1348726/telha_sanduiche_termo_acustica_trapezoidal_colorida_2_faces_preenchimento_isopor_256707237_2_1da381cdb04447f0157e143684754e63.png</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8483,7 +8987,11 @@
           <t>Telha de isopor termoacústica pintada de branco em duas faces.</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Preenchimento de isopor, pintura branca, 2 faces.</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8494,7 +9002,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1348726/telha_sanduiche_termo_acustica_trapezoidal_colorida_2_faces_preenchimento_isopor_256707237_4_526510fad9b9883b7e9477d8cb2f9040.png | https://acdn-us.mitiendanube.com/stores/621/456/products/meu_produto_pz40x1020_forro_eps_corexterna_branca_corinterna_branca_visao_externa-2cd9dcf3f84f405d0c17308958312336-640-0.jpg | https://acdn-us.mitiendanube.com/stores/621/456/products/meu_produto_pz40x1020_forro_eps_corexterna_branca_corinterna_branca_visao_interna-347052a5413590cde517308958278887-480-0.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8527,7 +9039,11 @@
           <t>Telha forro de isopor pintada com duas faces na cor branca.</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Material: Isopor; Cor: Branco; Faces: 2</t>
+        </is>
+      </c>
       <c r="H169" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8538,7 +9054,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>https://i0.wp.com/telhasprime.com.br/wp-content/uploads/2021/02/WhatsApp-Image-2021-05-05-at-11.34.57.jpeg?resize=1024,768&amp;ssl=1 | http://acdn-us.mitiendanube.com/stores/621/456/products/meu_produto_pz40x1020_forro_eps_corexterna_branca_corinterna_branca_visao_externa-2cd9dcf3f84f405d0c17308958312336-640-0.jpg | https://i1.wp.com/telhasprime.com.br/wp-content/uploads/2020/04/6.png?resize=554,417&amp;ssl=1</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8571,7 +9091,11 @@
           <t>Telha galvanizada trapezoidal pintada na cor preta, com uma face visível.</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Largura: 0,43 metros, Material: Aço galvanizado, Cor: Preta fosca, Tipo: Trapezoidal</t>
+        </is>
+      </c>
       <c r="H170" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -8582,7 +9106,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1318890/180_telha_pre_pintada_preta_fosco_tp40_0_43_metro_linear_3_65_19825_1_6f0465112a93c7a409e115a9b46ed66d.png | https://fabricaaqui.com.br/wp-content/uploads/2021/12/Telha-Trapezio-40-980-1020-Metalica-Ondulada-043-050-Sanduiche-Termo-Acustica-Trapezoidal-25-100-Dobrador-de-Perfil-Metalico-de-Aco-em-Chapa-U-Catanduva-Sao-Jose-do-Rio-Preto-Fernandopolis-Sp.jpeg | https://static.wixstatic.com/media/b78f78_cd399db912a64c6d91405676866d154f~mv2.png/v1/fill/w_980,h_980,al_c,q_90,usm_0.66_1.00_0.01,enc_avif,quality_auto/b78f78_cd399db912a64c6d91405676866d154f~mv2.png</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8630,7 +9158,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>https://galvtelhas.com.br/wp-content/uploads/elementor/thumbs/telha-trapezoidal-gt-0001-qcf7t2afb9nfoy3poxxlw21jpftj9dd6ng99trw9zc.jpg | https://telhasgoias.com.br/wp-content/uploads/2022/08/RT35-1050_site.png | https://termometais.com.br/wp-content/uploads/2022/03/tp-35-1050.png</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8678,7 +9210,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://i.ytimg.com/vi/du0zK12IRBc/maxresdefault.jpg | https://www.polysolution.com.br/v_2016/wp-content/uploads/2017/03/Thermopainel-transpasse-com-telha-termoacustica-em-Policarbonato-30-mm-Polysolution-4.jpg | https://construindodecor.com.br/wp-content/uploads/2019/10/Telha-Termoacustica-simples-768x432.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8726,7 +9262,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>https://telhaspontagrossa.com.br/wp-content/uploads/2022/10/tr-25-atual.png | https://telhasferrari.com.br/wp-content/uploads/2021/12/rotativo-telha-trapezio-25_1020-1536x525.png | https://telhasferrari.com.br/wp-content/uploads/2021/12/rotativo-telha-trapezio-25_1020-2048x700.png</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8754,7 +9294,11 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Água sanitária é um produto de limpeza e desinfecção amplamente utilizado para higienização de ambientes e superfícies.</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
@@ -8766,7 +9310,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>https://www.jjguimaraes.net/storage/2021/04/agua-sanitaria-1618002216.png | https://cdn.dooca.store/150/products/4483.jpg?v=1661957274&amp;webp=0 | https://inovainsumos.com.br/wp-content/uploads/2023/11/AGUA-SANITARIA-01LT-AUDAX.png</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8862,7 +9410,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_764368-MLA70435050496_072023-O.webp | https://down-br.img.susercontent.com/file/sg-11134201-7qvfx-lgfuwzl4cft256 | https://vertikalrepresentacoes.com.br/wp-content/uploads/2023/06/2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8906,7 +9458,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>https://hotmart.s3.amazonaws.com/product_pictures/0f757282-9e9f-4c44-b1d6-f2b849ffea85/EBOOK.png | https://i.ytimg.com/vi/mHNEoa0ugf4/maxresdefault.jpg | https://minio.scielo.br/documentstore/2316-8943/6wYZKrqNHPdnGn8NbfPRyCN/46907598046297136c2510992d45a48ce34c08cb.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8954,7 +9510,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_916316-MLB49301264555_032022-O.webp | https://cdn.awsli.com.br/800x800/31/31517/produto/238897283bc6e1b04ec.jpg | https://ecopolymerbr.com/cdn/shop/files/Alcool705l.jpg?v=1724855319&amp;width=1946</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8982,7 +9542,11 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>O produto ALUGUEIS refere-se a serviços de aluguel de produtos, possivelmente oferecidos por empresas como a Magazine Luiza.</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
@@ -8994,7 +9558,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr"/>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>https://i.ytimg.com/vi/4QXnygAfEfQ/maxresdefault.jpg | https://escolaeducacao.com.br/wp-content/uploads/2022/04/saiba-tudo-sobre-servico-de-aluguel-de-produtos-da-magalu.jpeg | https://cdnx.jumpseller.com/proevento/image/75112132/resize/1200/1200?1774452866</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9042,7 +9610,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/1244/1244673/produto/350604719/57x30-1-agi9816tdf.jpg | https://down-br.img.susercontent.com/file/br-11134207-7r98o-m7846i5clzd6e1 | https://lojaalfa.com/image/cache/catalog/scrity/021e71800f78f000f03050485b64fa35-1200x1200.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9090,7 +9662,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>https://auge-assets.nyc3.cdn.digitaloceanspaces.com/products/gallery/20909/bobina-termica-80mmx40m-branca-48g-101279-73767.jpg | https://http2.mlstatic.com/D_NQ_NP_934832-MLB97091563642_112025-O.webp | https://down-br.img.susercontent.com/file/br-11134201-22120-l5al6u909zkv65</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9138,7 +9714,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/894708/bom_ar_aerosol_lavanda_360_ml_295_1_93b021a2446de30ebfce90d25b88b919.jpg | https://www.l4limpeza.com.br/image/cache/catalog/911779833_BOMAR_360ML_LAVANDA-650x650.jpg | https://d8vlg9z1oftyc.cloudfront.net/tozzoalimentos/image/product/b01d387ba31ad2a394b717a555c5d24920200204152946/original/bom-ar-aero-lavanda-emb-econ-360ml_3303.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9215,7 +9795,11 @@
           <t>Calculadora Bobina HR 150 Casio, uma calculadora de bobina com funções básicas para uso comercial e financeiro.</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>12 dígitos, bivolt, cor preta, com bobina</t>
+        </is>
+      </c>
       <c r="H184" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9226,7 +9810,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1148871/calculadora_com_bobina_casio_hr150rc_12_digitos_bivolt_preto_1773_3_3c78c182dba3ad5ee7c3894757f952a7.jpg | https://www.accetecnologia.com.br/wp-content/uploads/2023/03/15152762553_CALCULADORA20COM20BOBINA20HR-150RC-B-DC-1.jpg | https://down-br.img.susercontent.com/file/4be7378329955f6b539c6284d99bfc9e</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9259,7 +9847,11 @@
           <t>Calculadora Bobina HR 150 Casio O NC, um modelo de calculadora com bobina para uso em escritórios e comércio.</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>12 dígitos, bivolt, cor preta, com bobina.</t>
+        </is>
+      </c>
       <c r="H185" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9270,7 +9862,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>https://product-hub-prd.madeiramadeira.com.br/1134724/images/62d36e72-6059-401b-97b3-32c82e41da1945832775calculadoracombobinacasiohr150tmbivoltean49718501748511800x800.jpg | https://http2.mlstatic.com/D_NQ_NP_953157-MLB92497308612_092025-O.webp | https://images.tcdn.com.br/img/img_prod/1148871/calculadora_com_bobina_casio_hr150rc_12_digitos_bivolt_preto_1773_3_3c78c182dba3ad5ee7c3894757f952a7.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9303,7 +9899,11 @@
           <t>Calculadora BPBINA HR150 com caso de proteção.</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>12 dígitos, bivolt, cor preta</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9314,7 +9914,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1148871/calculadora_com_bobina_casio_hr150rc_12_digitos_bivolt_preto_1773_3_3c78c182dba3ad5ee7c3894757f952a7.jpg | https://http2.mlstatic.com/D_NQ_NP_953157-MLB92497308612_092025-O.webp | https://gepelpapelaria.com.br/wp-content/uploads/2023/11/Design-sem-nome-13.png</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9362,7 +9966,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr"/>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>https://cdn.luxuryloyalty.com/media/product/list/faf505a9-47ce-4d2b-8261-2b0895521efe.jpg | https://milanimateriais.com.br/wp-content/uploads/2024/05/Slide38.png | https://armazemon.com.br/wp-content/uploads/2025/12/carrinho1-1.png</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9410,7 +10018,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/2439/2439447/produto/1972178772a91331f51.jpg | https://cdn.awsli.com.br/2500x2500/2439/2439447/produto/197217877/clips-1-koh20hvzcx.png | https://cdn.awsli.com.br/2500x2500/2439/2439447/produto/197217877/clips-2-nyeyutxs2y.png</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9443,7 +10055,11 @@
           <t>Cloro ativo 500 da marca Veja, produto utilizado para limpeza e desinfecção.</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Volume: 500 ml</t>
+        </is>
+      </c>
       <c r="H189" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -9454,7 +10070,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>https://loja.talimpo.com.br/sitecontent/ecommercex/produto/images/g/20062020071349_0940134__VEJA_LIMPEZA_PESADA_CLORO_ATIVO_500_ML.png | https://d2r9epyceweg5n.cloudfront.net/stores/001/060/518/products/multiuso-limpeza-pesada-cloro-ativo-500ml-veja1-e298e5c3452f53191f15923490112913-1024-1024.jpg | https://down-br.img.susercontent.com/file/br-11134207-81z1k-mf5ktaaoszra1e</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9498,7 +10118,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>https://www.braskem.com.br/portal/principal/2022/img/banner-combustivel.jpg | https://www.paixaoporcombustao.com.br/wp-content/uploads/2024/12/tipos-de-combustiveis-Paixao-por-combustao-1018x1024.jpg | http://www.franciscolaianunes.com/media/mvddfmdz/file128-3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9542,7 +10166,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>https://sac.m8sistemas.com/galleryDocuments/edbsnfd51dcc1f74ec7554a257a861f242290ad21b5fe859e4469395178aab6e2503f35471db9a2b5ef05a8e44999ccfecab7 | https://centraldeatendimento.totvs.com/hc/article_attachments/4424098086167/mceclip10.png | https://wiki.centrium.com.br/wp-content/uploads/sites/2/2021/11/image-5-768x793.png</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9570,7 +10198,11 @@
           <t>GERAL</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>O produto 'Conhecimento de Frete' parece ser um documento ou serviço relacionado à logística e transporte de mercadorias, mas não há informações detalhadas disponíveis.</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
@@ -9582,7 +10214,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>https://gritsch.com.br/wp-content/uploads/2023/04/Gritsch-Tipos-de-Frete.jpg | https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEjwtYUvW4gr-c2pgchWMfSjCmzdSOzOUkIm1Uh3zH81zbLuFKa58oBFie9vVovOQHLgrdqc2QsERDfx8XzquESNN4SEqQ0N-_2rGwUb_4LMeR6U9XUhbIYawq5JE9XC-OVDq3osR7l8xNgWrxXYeEgSEHWPMY50WRtpRW1q7LCizfmc9yPnAC01XqUhx6DR/s1377/Imagem2.png | https://bdc.ideiatecnologia.com.br/wp/wp-content/uploads/2024/07/Captura-de-tela-2024-07-31-125916.png</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9630,7 +10266,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/600x700/2416/2416225/produto/280036619/cfd8eeb77acf9a74201739a1d22f6418-hd2e05z5j9.jpg | https://lembreiquetem.com.br/wp-content/uploads/2024/06/Corretivo-Liquido-atima-18ml-Radex-1190756942.png | https://cdn.sistemawbuy.com.br/arquivos/c2c00f215d1d296edc13d220cd13f9a7/produtos/6911e1133e83a/6-6911e26be60d0.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9674,7 +10314,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>https://lirp.cdn-website.com/72d4af81/dms3rep/multi/opt/Créditos-de-ICMS_1-1920w.webp | https://verot.com.br/wp-content/uploads/2026/05/Blog-ICMS-Banner-1024x576.jpg | https://media.licdn.com/dms/image/v2/D4D22AQG263DVL5ff6w/feedshare-shrink_2048_1536/feedshare-shrink_2048_1536/0/1689710230539?e=2147483647&amp;v=beta&amp;t=XhHwIAKIMfaW76mN4XnFtLQFEfYhSVe-Bc4xukKV9yQ</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9770,7 +10414,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>https://kbvaco.com.br/wp-content/uploads/2022/11/35-1-768x768.png | https://barataodatelha.com.br/wp-content/uploads/2022/11/Site_Baratao_Cumeeira-1024x1024.png | https://acokrr.com.br/wp-content/uploads/2021/11/cumeeira.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9818,7 +10466,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-7r98o-lvumdx2itncmda | https://a-static.mlcdn.com.br/618x463/desinfetante-lysoform-bruto-5l/magazineluiza/223306600/b2af546eb7d73a3a302a1ec115b49e04.jpg | https://www.contabilista.com.br/media/catalog/product/cache/e7bd975ee72b2e17c1d729a77564a9f3/0/1/0101028B.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9866,7 +10518,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr"/>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>https://beagaembalagem.com.br/wp-content/uploads/2014/09/detergente-ype-500-ml.jpg | https://images.tcdn.com.br/img/img_prod/880282/detergente_neutro_ype_500_ml_1059_1_6858b320c10f7e389fefdf0efd780951.jpg | https://quimicarocha.com.br/wp-content/uploads/2024/01/DETERGENTE-YPE-1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9914,7 +10570,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr"/>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>https://icaraidobrasil.com.br/wp-content/uploads/2022/04/Detergente-Limao-500ml_icarai.jpg | https://www.dellys.com.br/ccstore/v1/images/?source=/file/v6070410447523333259/products/83928.imagem1.JPG&amp;height=940&amp;width=940 | https://www.sondadelivery.com.br/img.aspx/sku/27804/530/7891022637007-(1).jpg</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9958,7 +10618,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr"/>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>https://dingo.com.br/wp-content/uploads/2022/04/operacao-icms-com-substituicao-tributaria.jpg | https://notafiscal.cnt.br/wp-content/uploads/2024/08/devolucao-com-substituicao-tributaria-cfop-icms-st-768x341.png | https://imgv2-2-f.scribdassets.com/img/document/733228343/original/76d8d6f968/1?v=1</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10002,7 +10666,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr"/>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>https://www.helexia.com.br/wp-content/uploads/2023/01/10_BLOG_HELEXIA_EXPANSAO-1-1536x696.png | https://d28w5jlx3m10k.cloudfront.net/wp-content/uploads/2026/05/unnamed-13-1024x683.png | https://d28w5jlx3m10k.cloudfront.net/wp-content/uploads/2024/09/energia-eletrica-600x345.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10046,7 +10714,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr"/>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>https://phygital-files.mercafacil.com/redeavistaooliveira/uploads/produto/esponja_condor_multiuso_l4_p3_5d979367-056a-443d-9b05-48e097151dad.jpg | https://esthampa.com.br/wp-content/uploads/2024/03/3871.png | https://down-br.img.susercontent.com/file/67259d26ab79d3c95920ffa4552f48ce</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10090,7 +10762,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr"/>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/586385/esponja_multiuso_brilhus_com_4_unidades_bettanin_20628_1_c5f72a16a1f1bffbee22dce81e389639.png | https://destro.fbitsstatic.net/img/p/esponja-brilhus-bettanin-multiuso-70176/256712-1.jpg?w=1000&amp;h=1000&amp;v=no-change&amp;qs=ignore | https://distribuidorafragueiro.com.ar/wp-content/uploads/2021/07/Esponja-Brilhus-Multiuso-Bettanin-1-342947.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10134,7 +10810,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_881335-MLB72901052759_112023-O.webp | https://cdn.awsli.com.br/800x800/2761/2761156/produto/299450525/captura-de-tela-2024-08-29-180321-qj5mp2l69y.jpg | https://http2.mlstatic.com/D_NQ_NP_839673-MLB72824533128_112023-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10182,7 +10862,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr"/>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>https://steffen.com.br/wp-content/uploads/2022/12/419-scaled.jpg | https://down-br.img.susercontent.com/file/sg-11134201-7rdwj-mckr7p8z3liv4e | https://cdn-cosmos.bluesoft.com.br/products/7891035618567</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10230,7 +10914,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>https://destro.fbitsstatic.net/img/p/limpador-perfumado-casa-e-perfume-passione-500ml-72618/259154.jpg?w=1000&amp;h=1000&amp;v=202501231555&amp;qs=ignore | https://destro.fbitsstatic.net/img/p/limpador-perfumado-casa-e-perfume-intuizione-500ml-70454/256990-1.jpg?w=1000&amp;h=1000&amp;v=202501231555&amp;qs=ignore | https://estreladistribuicao.agilecdn.com.br/130514.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10322,7 +11010,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr"/>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://feiradaborrachacampinas.com.br/wp-content/uploads/2023/12/2-3-2.png | https://escontrol.com.br/wp-content/uploads/2023/12/3-min-13.png | https://mackflex.com.br/wp-content/uploads/2022/12/produto-de-manutencao-industrial.png</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10366,7 +11058,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr"/>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>https://medequipa.com.br/system/filemanager/files/produtos_anexos_1_11_46_1561402779.jpg | https://0701.static.prezi.com/preview/v2/r4wffstuxp6a7uojjhajohijnp6jc3sachvcdoaizecfr3dnitcq_3_0.png | https://i.ytimg.com/vi/8BLnXnLbg1A/maxresdefault.jpg?sqp=-oaymwEmCIAKENAF8quKqQMa8AEB-AH-CYAC0AWKAgwIABABGD8gTyh_MA8=&amp;rs=AOn4CLAD4vdQ47bxK3uw_23wV6OkEx5Trg</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10414,7 +11110,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>https://gscdistrilimp.com.br/wp-content/uploads/2022/11/D_NQ_NP_674481-MLB31854442650_082019-O.jpg | https://cdn.awsli.com.br/600x700/2702/2702421/produto/299083909/veja-multi-uso-tradicional-500ml-d10e23c1-dt7onxxwyb.jpeg | https://irmaosbrant.com.br/2589-large_default/veja-multiuso-com-alcool.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10462,7 +11162,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr"/>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/739678/limpador_multiuso_veja_tradicional_500ml_2333_1_9fc656b2ae4e0de2c1eee5e9bf32e1f7.jpg | https://casacoqueiro.com.br/wp-content/uploads/2023/11/1108.jpg | https://everlimp.com.br/wp-content/uploads/2021/05/foto00-132-scaled-1-600x900-1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10495,7 +11199,11 @@
           <t>Oodorizador de ambiente, produto para eliminar odores e deixar um aroma agradável.</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Volume: 400ml, Peso: 240g</t>
+        </is>
+      </c>
       <c r="H212" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -10506,7 +11214,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134201-23030-ykrc3gzbgrov3e | https://down-br.img.susercontent.com/file/br-11134207-7r98o-mcv4f2xjcppue8 | https://cdn.awsli.com.br/2500x2500/1623/1623042/produto/354526770/odorizador-de-ambientes-floral-400ml240g-yabgcb3i93.png</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10554,7 +11266,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-81z1k-mhh0w8hnwj5yb6 | https://down-br.img.susercontent.com/file/br-11134207-7r98o-m9elgz108pixf2 | https://down-br.img.susercontent.com/file/br-11134207-81z1k-mgpc8aruo7456e</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10602,7 +11318,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-7r98o-ll3jgwi5pqv0ba | https://down-br.img.susercontent.com/file/br-11134207-7r98o-m9elgz108pixf2 | https://cdn.awsli.com.br/600x700/1356/1356487/produto/274145263/pano-chao-0202-vrbxsapbve.png</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10650,7 +11370,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-81z1k-meiqhvvvahvnc1 | https://down-br.img.susercontent.com/file/br-11134207-7qukw-lje55qykhxv405 | https://down-br.img.susercontent.com/file/br-11134207-7r98o-m3ko8pcpwdh405</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10698,7 +11422,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/1358/1358824/produto/227798860743b52c3e1.jpg | https://cdn.iset.io/assets/48768/produtos/1577/pano-multiuso-rolo-azul-28x300m-nobre-01.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10746,7 +11474,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://lojapapelex.vtexassets.com/arquivos/ids/211072/papel-toalha-interf-20x21-brluxo-papelex-01.jpg?v=637897123792830000 | https://http2.mlstatic.com/D_NQ_NP_935767-MLB78562165238_082024-O-papel-toalha-interfolha-branco-luxo-premium-20x21-10000-fls.webp | https://images.tcdn.com.br/img/img_prod/1025931/papel_toalha_20x21_interfolha_luxo_branco_c_1000_smartpell_1961_1_4442b5febc2a5e691f56e21d701873bf.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10794,7 +11526,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://cdn.sistemawbuy.com.br/arquivos/9e5e7e91a848f7c209e19f8d775f1ee4/produtos/67815a7704f49/4695-a-6892085e3b2fc.jpg | https://images.tcdn.com.br/img/img_prod/1165337/papel_chamex_a4_75g_m_210mm_x_297mm_office_branco_500_folhas_15085_1_85451bcfeacce8a954a3af8b3157b65c.jpg | https://cdn.awsli.com.br/600x700/2695/2695431/produto/372880496/pqd3uqq8_t-0ue1rac3rw.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10842,7 +11578,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/c4d9c755d3b422df90dceeff460c2881 | https://fabesul.com.br/wp-content/uploads/2025/11/32201.jpg | https://images.tcdn.com.br/img/img_prod/1250632/papel_chamex_office_a4_75g_c_500_folhas_6011_1_bb899586557a4e05e9ec73bdea2d2d2d.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10890,7 +11630,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_659254-MLA99338098426_112025-O.webp | https://d5gag3xtge2og.cloudfront.net/producao/35874481/G/nobre.jpg | https://http2.mlstatic.com/D_NQ_NP_706213-MLB84966181443_052025-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10930,7 +11674,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://suporte.senior.com.br/attachments/token/B5thED8x9cN982nY71xgoKpYe/?name=image.png | http://2.bp.blogspot.com/-hzePMy_Y9Bg/U4506eD9dQI/AAAAAAAAAXs/l0W4KXkvx2Q/s1600/níveis+de+produto.png | https://www.slideteam.net/wp/wp-content/uploads/2023/09/Visao-geral-do-produto-–-principais-recursos-e-precos-3.png</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10978,7 +11726,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr"/>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/600x1000/2525/2525048/produto/382928287/download-7ll4i0unf7.jpg | https://cdn.awsli.com.br/2500x2500/2703/2703882/produto/25737208157205145e3.jpg | https://images.tcdn.com.br/img/img_prod/880282/deoline_erva_doce_sabonete_liquido_premisse_5_litros_1309_1_42f7f0f0ba55546fe6229d5250989136.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11011,7 +11763,11 @@
           <t>Sabonete líquido em embalagem de 5 litros.</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Volume: 5 litros, Tipo: Neutro, Composição: Glicerinado</t>
+        </is>
+      </c>
       <c r="H223" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -11022,7 +11778,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>https://melhoramentoshigiene.com.br/wp-content/uploads/2022/10/207446.png | https://images.tcdn.com.br/img/img_prod/788764/sabonete_liquido_5_litros_neutro_glicerinado_premisse_1903_1_7cc7ecafbffd7b6f80a3221e7d6b47a1.jpg | https://down-br.img.susercontent.com/file/sg-11134201-7rdwn-lylbcnckfvlj47</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11114,7 +11874,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J225" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-7r98o-lwa16pkbil5e32 | https://down-br.img.susercontent.com/file/sg-11134201-8258p-mg9dxd1wcvt68b | https://down-br.img.susercontent.com/file/br-11134207-7r98o-lt71a4w71x2s83</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11162,7 +11926,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-7r98o-m321kdvu7pp124 | https://down-br.img.susercontent.com/file/sg-11134201-7rate-mak4zuhtzij42c | https://www.l4limpeza.com.br/image/cache/catalog/910976125_100UNID_60L_PRETO_TP-800x800.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11206,7 +11974,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>https://i.ytimg.com/vi/fMLHZFQ8ZyE/maxresdefault.jpg | https://flexmethod4innovation.com/wp-content/uploads/2021/11/MFfig466-terminologia-produto-x-servico.png | https://vedanaassociados.com.br/wp-content/uploads/2021/06/banner_produtos_servicos.png</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11250,7 +12022,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>https://datacaixa.com.br/wp-content/uploads/2025/03/Taxa-de-Entrega-por-KM_Taxa.png | https://datacaixa.com.br/wp-content/uploads/2023/11/17-Configuracao-Taxa-Entrega-1.png | https://cardapioweb.com/blog/wp-content/uploads/2024/07/Como-calcular-a-taxa-de-entrega-ideal-no-delivery.png</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11294,7 +12070,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J229" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134201-23030-xukt7t7e4dov43 | https://cdn.awsli.com.br/2500x2500/515/515028/produto/278817686/18078-2-znhjw5nhgh.jpg | https://a-static.mlcdn.com.br/800x560/teclado-usb-game-kg-10bk-c3t-c3-tech/compraokmatriz/1259/d75dbaef729deeea2fed09eaf856c3b3.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11338,7 +12118,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>https://esthec.com.br/wp-content/uploads/2022/01/Telefone-Com-Fio-Intelbras-Pleno-Preto.jpg | https://joli.vtexassets.com/arquivos/ids/611531/Telefone_Pleno_Preto_Intelbras_101180001jpg.jpg?v=638026221870530000 | https://down-br.img.susercontent.com/file/br-11134207-7r98o-m57k9ne6vq85fb</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11386,7 +12170,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>https://grupocasalima.com/wp-content/uploads/2023/09/s_costura-Sch-40.webp | https://www.vaneco.com.pe/assets/uploads/producto_tubo_inox_con_costura.png | https://http2.mlstatic.com/D_NQ_NP_693104-MLB52125871045_102022-O-tubo-aco-carbono-sch-40-astm-a-178-grau-a-scostura-dn-6.webp</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
